--- a/procesos_armada.xlsx
+++ b/procesos_armada.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F97"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,22 +463,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>38/3-0429-LPU26</t>
+          <t>92-0006-LPU26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN BOTES NEUMÁTICOS</t>
+          <t>DIGITALIZACIÓN DEL ARCHIVO DE PUBLICACIONES PERIÓDICAS DE LA EDITORIAL SARMIENTO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>38/03 - UOC de la Intendencia Naval Puerto Belgrano - Armada Argentina</t>
+          <t>92 - Departamento de Compras y Contrataciones- BN</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>38/03 - UOC de la Intendencia Naval Puerto Belgrano - Armada Argentina</t>
+          <t>92 - Departamento de Compras y Contrataciones- BN</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -488,29 +488,29 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>14/9/2026</t>
+          <t>16/9/2026</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>487-0076-LPU26</t>
+          <t>68-0010-LPU26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Adquisición de ambos y guardapolvos para el Complejo Médico CHURRUCA-VISCA</t>
+          <t>SERVICIO DE SEGURIDAD Y VIGILANCIA EN CAMPO DE INMUNIZACIONES MARCOS PAZ - INPB</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>487 - División Compras y Suministros - Superintendencia de Bienestar de la Policia Federal Argentina</t>
+          <t>68/00 - Departamento de Administracion de Bienes - ANLIS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>487 - División Compras y Suministros - Superintendencia de Bienestar de la Policia Federal Argentina</t>
+          <t>68/00 - Departamento de Administracion de Bienes - ANLIS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -520,29 +520,29 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>14/9/2026</t>
+          <t>16/9/2026</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>72-0022-LPU26</t>
+          <t>315-0014-LPU26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE EQUIPO, MATERIAL INFORMÁTICO Y UN SISTEMA INTEGRAL DE REPRESENTACIÓN PARA EL EMCFFAA</t>
+          <t>Servicio de provisión e instalación de 1100 metros cuadrados (m2) de piso de goma</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>72/00 - Dirección Administrativa Financiera- EMCFFAA- Dpto de contrataciones</t>
+          <t>315/000 - Dirección General de Administración - MP</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>72/00 - Dirección Administrativa Financiera- EMCFFAA- Dpto de contrataciones</t>
+          <t>315/000 - Dirección General de Administración - MP</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -552,29 +552,29 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>14/9/2026</t>
+          <t>16/9/2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>84/30-0665-LPU26</t>
+          <t>21-0023-LPU26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CONTRATAR UN SERVICIO DE MANTENIMIENTO Y REPARACIÓN DE EDIFICIOS - LMGP</t>
+          <t>SERVICIO DE MANTENIMIENTO EQUIPOS DE AIRE ACONDICIONADO EN LA SEDE CENTRAL Y AMBA DE LA DNM.-</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>84/30 - Liceo Militar General Paz</t>
+          <t>21/000 - Dirección General de Administración - DNM</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>84/30 - Liceo Militar General Paz</t>
+          <t>21/000 - Dirección General de Administración - DNM</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -584,29 +584,29 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>15/9/2026</t>
+          <t>16/9/2026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>101-0006-LPU26</t>
+          <t>47-0005-LPU26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Serv de impermeabilización ext, pintura 4 y 5 piso e instalación, ensayo y certificación anclajes</t>
+          <t>Contratación seguro para los buques de investigación pesquera del INIDEP</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>101 - Departamento de Compras y Contrataciones</t>
+          <t>47 - Dpto. de Compras y Servicios- INIDEP</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>101 - Departamento de Compras y Contrataciones</t>
+          <t>47 - Dpto. de Compras y Servicios- INIDEP</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -616,29 +616,29 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>15/9/2026</t>
+          <t>16/9/2026</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>84/26-0667-LPU26</t>
+          <t>52-0044-LPU26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SERVICIO DE SINGLE TEST PARA BIOLOGIA MOLECULAR Y SEROLOGIA</t>
+          <t>CONTRATACIÓN DE UN (1) SERVICIO PROFESIONAL PARA ACTUALIZACIÓN Y EVOLUCIÓN FUNCIONAL SISTEMA SIGCER</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>84/26 - Hospital Militar Central 601</t>
+          <t>52 - Coordinación de Compras y Contrataciones - SENASA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>84/26 - Hospital Militar Central 601</t>
+          <t>52 - Coordinación de Compras y Contrataciones - SENASA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -648,29 +648,29 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>15/9/2026</t>
+          <t>16/9/2026</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>92-0006-LPU26</t>
+          <t>64-0019-LPU26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DIGITALIZACIÓN DEL ARCHIVO DE PUBLICACIONES PERIÓDICAS DE LA EDITORIAL SARMIENTO</t>
+          <t>Adquisición de Computadoras de Escritorio tipo AIO y Monitores para la S.R.T.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>92 - Departamento de Compras y Contrataciones- BN</t>
+          <t>64/000 - Departamento de Compras y Contrataciones- SRT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>92 - Departamento de Compras y Contrataciones- BN</t>
+          <t>64/000 - Departamento de Compras y Contrataciones- SRT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -687,22 +687,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>68-0010-LPU26</t>
+          <t>38/3-0440-LPU26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SERVICIO DE SEGURIDAD Y VIGILANCIA EN CAMPO DE INMUNIZACIONES MARCOS PAZ - INPB</t>
+          <t>CONCESIÓN ONEROSA DEL SERVICIO DE BUFFET Y CANTINA DEL ESTADIO DE DEPORTES DE LA BNPB.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>68/00 - Departamento de Administracion de Bienes - ANLIS</t>
+          <t>38/03 - UOC de la Intendencia Naval Puerto Belgrano - Armada Argentina</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>68/00 - Departamento de Administracion de Bienes - ANLIS</t>
+          <t>38/03 - UOC de la Intendencia Naval Puerto Belgrano - Armada Argentina</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -719,22 +719,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>315-0014-LPU26</t>
+          <t>68-0011-LPU26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Servicio de provisión e instalación de 1100 metros cuadrados (m2) de piso de goma</t>
+          <t>Contratación del Servicio de limpieza edilicia -INE (Alcanzado por el Protocolo del Mercosur)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>315/000 - Dirección General de Administración - MP</t>
+          <t>68/00 - Departamento de Administracion de Bienes - ANLIS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>315/000 - Dirección General de Administración - MP</t>
+          <t>68/00 - Departamento de Administracion de Bienes - ANLIS</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -744,29 +744,29 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>16/9/2026</t>
+          <t>17/9/2026</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>21-0023-LPU26</t>
+          <t>78-0010-LPU26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENIMIENTO EQUIPOS DE AIRE ACONDICIONADO EN LA SEDE CENTRAL Y AMBA DE LA DNM.-</t>
+          <t>Adquisición de sobres para ensobrado manual de pasaportes y DNI</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>21/000 - Dirección General de Administración - DNM</t>
+          <t>78/000 - División Compras</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>21/000 - Dirección General de Administración - DNM</t>
+          <t>78/000 - División Compras</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>16/9/2026</t>
+          <t>17/9/2026</t>
         </is>
       </c>
     </row>
@@ -815,22 +815,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>84/129-0670-LPU26</t>
+          <t>347-0028-LPU26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE PINTURAS Y ARTÍCULOS DE FERRETERÍA PARA EL B ARS 604</t>
+          <t>CONTRATACIÓN DE MANO DE OBRA ESPECIALIZADA Y ADQUISICIÓN DE REPUESTOS PARA EL HELICOPTERO AW169</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>84/129 - Dirección de Arsenales</t>
+          <t>347/000 - Dirección General de Administración - MS</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>84/129 - Dirección de Arsenales</t>
+          <t>347/000 - Dirección General de Administración - MS</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -840,29 +840,29 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>16/9/2026</t>
+          <t>17/9/2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>47-0005-LPU26</t>
+          <t>78-0011-LPU26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Contratación seguro para los buques de investigación pesquera del INIDEP</t>
+          <t>Contratación del servicio de mantenimiento, reparación e instalación de aires acondicionados.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>47 - Dpto. de Compras y Servicios- INIDEP</t>
+          <t>78/000 - División Compras</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>47 - Dpto. de Compras y Servicios- INIDEP</t>
+          <t>78/000 - División Compras</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -872,29 +872,29 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>16/9/2026</t>
+          <t>17/9/2026</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>52-0044-LPU26</t>
+          <t>79/8-0006-LPU26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN DE UN (1) SERVICIO PROFESIONAL PARA ACTUALIZACIÓN Y EVOLUCIÓN FUNCIONAL SISTEMA SIGCER</t>
+          <t>Servicio integral llave en mano Ceremonia de los Best Tourism Villages de ONU Turismo 2026</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>52 - Coordinación de Compras y Contrataciones - SENASA</t>
+          <t>79/8 - SAF322 - SECRETARIA DE AMBIENTE Y TURISMO</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>52 - Coordinación de Compras y Contrataciones - SENASA</t>
+          <t>79/8 - SAF322 - SECRETARIA DE AMBIENTE Y TURISMO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -904,29 +904,29 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>16/9/2026</t>
+          <t>18/9/2026</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>64-0019-LPU26</t>
+          <t>38/3-0443-LPU26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Adquisición de Computadoras de Escritorio tipo AIO y Monitores para la S.R.T.</t>
+          <t>CONCESIÓN ONEROSA DEL SERVICIO DE BUFFET Y CANTINA DEL CLUB GOLF DE PUERTO BELGRANO (BNPB)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>64/000 - Departamento de Compras y Contrataciones- SRT</t>
+          <t>38/03 - UOC de la Intendencia Naval Puerto Belgrano - Armada Argentina</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>64/000 - Departamento de Compras y Contrataciones- SRT</t>
+          <t>38/03 - UOC de la Intendencia Naval Puerto Belgrano - Armada Argentina</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -936,29 +936,29 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>16/9/2026</t>
+          <t>18/9/2026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>38/3-0440-LPU26</t>
+          <t>340/1-0054-LPU26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CONCESIÓN ONEROSA DEL SERVICIO DE BUFFET Y CANTINA DEL ESTADIO DE DEPORTES DE LA BNPB.</t>
+          <t>ADQUISICIÓN DE REPUESTOS DE BASE - SOSTÉN LOGÍSTICO ANTÁRTICO.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>38/03 - UOC de la Intendencia Naval Puerto Belgrano - Armada Argentina</t>
+          <t>340/001 - Dirección General de Administración - SSSLD</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>38/03 - UOC de la Intendencia Naval Puerto Belgrano - Armada Argentina</t>
+          <t>340/001 - Dirección General de Administración - SSSLD</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -968,29 +968,29 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>16/9/2026</t>
+          <t>18/9/2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>46-0037-LPU26</t>
+          <t>38/19-0445-LPU26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Concesión de uso precario y exclusivo del espacio rel a la DNV P/ Viandas Desayunos y Meriendas.</t>
+          <t>DGED ADQUISICIÓN DE DOS SIMULADORES DE TIRO</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>46/000 - Coordinación de Licitaciones y Contrataciones - DNV</t>
+          <t>38/19 - División Contrataciones del Cuartel General del EMGA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>46/000 - Coordinación de Licitaciones y Contrataciones - DNV</t>
+          <t>38/19 - División Contrataciones del Cuartel General del EMGA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1000,29 +1000,29 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>17/9/2026</t>
+          <t>21/9/2026</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>68-0011-LPU26</t>
+          <t>84/24-0677-LPU26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Contratación del Servicio de limpieza edilicia -INE (Alcanzado por el Protocolo del Mercosur)</t>
+          <t>ALQUILER DE EQUIPOS DE FOTOCOPIADO DIGITAL E IMPRESORAS, SU MANTENIMIENTO INTEGRAL E INSUMOS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>68/00 - Departamento de Administracion de Bienes - ANLIS</t>
+          <t>84/24 - Colegio Militar de la Nación - Compras y Contrataciones</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>68/00 - Departamento de Administracion de Bienes - ANLIS</t>
+          <t>84/24 - Colegio Militar de la Nación - Compras y Contrataciones</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1032,29 +1032,29 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>17/9/2026</t>
+          <t>21/9/2026</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>78-0010-LPU26</t>
+          <t>38/6-0447-LPU26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Adquisición de sobres para ensobrado manual de pasaportes y DNI</t>
+          <t>RECAMBIO Y READECUACION INTEGRAL DEL SISTEMA DE CALEFACCION DEL EDIFICIO COMANDO DEL BIM4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>78/000 - División Compras</t>
+          <t>38/6 - INTENDENCIA NAVAL USHUAIA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>78/000 - División Compras</t>
+          <t>38/6 - INTENDENCIA NAVAL USHUAIA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1064,29 +1064,29 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>17/9/2026</t>
+          <t>21/9/2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>347-0028-LPU26</t>
+          <t>39-0039-LPU26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN DE MANO DE OBRA ESPECIALIZADA Y ADQUISICIÓN DE REPUESTOS PARA EL HELICOPTERO AW169</t>
+          <t>REPARACIÓN INTEGRAL DEL GUARDACOSTAS PNA GC-65 “MARTÍN GARCIA”.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>347/000 - Dirección General de Administración - MS</t>
+          <t>39 - Dirección General de Administración- PNA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>347/000 - Dirección General de Administración - MS</t>
+          <t>39 - Dirección General de Administración- PNA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1096,29 +1096,29 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>17/9/2026</t>
+          <t>22/9/2026</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>78-0011-LPU26</t>
+          <t>68-0012-LPU26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Contratación del servicio de mantenimiento, reparación e instalación de aires acondicionados.</t>
+          <t>INSTALACION DE ALAMBRADO Y DEFORESTACIÓN EN CAMPO ANEXO - INPB (ALCANZADO POR PROTOCOLO MERCOSUR)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>78/000 - División Compras</t>
+          <t>68/00 - Departamento de Administracion de Bienes - ANLIS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>78/000 - División Compras</t>
+          <t>68/00 - Departamento de Administracion de Bienes - ANLIS</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1128,29 +1128,29 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>17/9/2026</t>
+          <t>22/9/2026</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>84/129-0675-LPU26</t>
+          <t>38/12-0453-LPU26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ADQUISICION DE REPUESTOS PARA PROGRAMAS DE MANTENIMIENTO DE 2do NIVEL B ARS 601, 602 Y 603</t>
+          <t>ADQUISICION DE CONJUNTOS BOMBAS DE TIMON PARA UNIDADES DEPENDIENTES DE LA DVCB.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>84/129 - Dirección de Arsenales</t>
+          <t>38/12 - Comando de la Flota de Mar</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>84/129 - Dirección de Arsenales</t>
+          <t>38/12 - Comando de la Flota de Mar</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1160,29 +1160,29 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>18/9/2026</t>
+          <t>23/9/2026</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>79/8-0006-LPU26</t>
+          <t>37/2-0092-LPU26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Servicio integral llave en mano Ceremonia de los Best Tourism Villages de ONU Turismo 2026</t>
+          <t>SERVICIO DE EXTRACCIÓN, TRASPORTE, MANTENIMIENTO Y LIMPIEZA RED CLOACAL DE LA GUARNICIÓN CENTINELA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>79/8 - SAF322 - SECRETARIA DE AMBIENTE Y TURISMO</t>
+          <t>37/002 - Unidad Tecnica Administrativa Contable Digeapoyo</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>79/8 - SAF322 - SECRETARIA DE AMBIENTE Y TURISMO</t>
+          <t>37/002 - Unidad Tecnica Administrativa Contable Digeapoyo</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1192,29 +1192,29 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>18/9/2026</t>
+          <t>23/9/2026</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>40/28-0162-LPU26</t>
+          <t>340/1-0056-LPU26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MANTENIMIENTO Y REPARACIÓN DE BANCO ESTÁTICO Y DE ARRASTRE</t>
+          <t>ADQUISICIÓN DE COMBUSTIBLE RADA LA PLATA - SOSTÉN LOGÍSTICO ANTÁRTICO</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>40/028 - AREA DE MATERIAL "RIO IV"</t>
+          <t>340/001 - Dirección General de Administración - SSSLD</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>40/028 - AREA DE MATERIAL "RIO IV"</t>
+          <t>340/001 - Dirección General de Administración - SSSLD</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1224,29 +1224,29 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>18/9/2026</t>
+          <t>23/9/2026</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>38/3-0443-LPU26</t>
+          <t>38/15-0462-LPU26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CONCESIÓN ONEROSA DEL SERVICIO DE BUFFET Y CANTINA DEL CLUB GOLF DE PUERTO BELGRANO (BNPB)</t>
+          <t>Adquisición de conservas y panificados para los destinos con asiento en IBPB - 1° TRIMESTRE 2027</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>38/03 - UOC de la Intendencia Naval Puerto Belgrano - Armada Argentina</t>
+          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>38/03 - UOC de la Intendencia Naval Puerto Belgrano - Armada Argentina</t>
+          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1256,29 +1256,29 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>18/9/2026</t>
+          <t>24/9/2026</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>340/1-0054-LPU26</t>
+          <t>38/15-0463-LPU26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE REPUESTOS DE BASE - SOSTÉN LOGÍSTICO ANTÁRTICO.</t>
+          <t>Adquisición de víveres secos y condimentos para los destinos con asiento en IBPB - 1° TRIMESTRE 2027</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>340/001 - Dirección General de Administración - SSSLD</t>
+          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>340/001 - Dirección General de Administración - SSSLD</t>
+          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1288,29 +1288,29 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>18/9/2026</t>
+          <t>24/9/2026</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>38/19-0445-LPU26</t>
+          <t>38/15-0464-LPU26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DGED ADQUISICIÓN DE DOS SIMULADORES DE TIRO</t>
+          <t>Obtención de lácteos y fiambre para los destinos con asiento en la IBBA (1er Trimestre 2027)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>38/19 - División Contrataciones del Cuartel General del EMGA</t>
+          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>38/19 - División Contrataciones del Cuartel General del EMGA</t>
+          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1320,29 +1320,29 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>21/9/2026</t>
+          <t>24/9/2026</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>84/24-0677-LPU26</t>
+          <t>38/15-0468-LPU26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ALQUILER DE EQUIPOS DE FOTOCOPIADO DIGITAL E IMPRESORAS, SU MANTENIMIENTO INTEGRAL E INSUMOS</t>
+          <t>Obtención de víveres secos y condimentos (1er TRIMESTRE) para los destinos con asiento en IBBA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>84/24 - Colegio Militar de la Nación - Compras y Contrataciones</t>
+          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>84/24 - Colegio Militar de la Nación - Compras y Contrataciones</t>
+          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1352,29 +1352,29 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>21/9/2026</t>
+          <t>24/9/2026</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>38/6-0447-LPU26</t>
+          <t>38/4-0469-LPU26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RECAMBIO Y READECUACION INTEGRAL DEL SISTEMA DE CALEFACCION DEL EDIFICIO COMANDO DEL BIM4</t>
+          <t>SERVICIO DE REPARACIÓN E IMPERMEABILIZACIÓN DE LOS TECHOS DEL ARSENAL NAVAL MAR DEL PLATA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>38/6 - INTENDENCIA NAVAL USHUAIA</t>
+          <t>38/4 - INTENDENCIA NAVAL MAR DEL PLATA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>38/6 - INTENDENCIA NAVAL USHUAIA</t>
+          <t>38/4 - INTENDENCIA NAVAL MAR DEL PLATA</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1384,29 +1384,29 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>21/9/2026</t>
+          <t>24/9/2026</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>39-0039-LPU26</t>
+          <t>38/15-0470-LPU26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>REPARACIÓN INTEGRAL DEL GUARDACOSTAS PNA GC-65 “MARTÍN GARCIA”.</t>
+          <t>Obtención de cortes cárnicos y huevos para los destinos con asiento en la IBBA (1er Trimestre 2027)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>39 - Dirección General de Administración- PNA</t>
+          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>39 - Dirección General de Administración- PNA</t>
+          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1416,29 +1416,29 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>22/9/2026</t>
+          <t>24/9/2026</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>68-0012-LPU26</t>
+          <t>38/15-0471-LPU26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>INSTALACION DE ALAMBRADO Y DEFORESTACIÓN EN CAMPO ANEXO - INPB (ALCANZADO POR PROTOCOLO MERCOSUR)</t>
+          <t>Adquisición de cortes cárnicos, cerdo, filet de merluza, pollo y huevo fresco para IBPB - 1° T 2027</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>68/00 - Departamento de Administracion de Bienes - ANLIS</t>
+          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>68/00 - Departamento de Administracion de Bienes - ANLIS</t>
+          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1448,29 +1448,29 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>22/9/2026</t>
+          <t>24/9/2026</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>38/12-0453-LPU26</t>
+          <t>38/6-0473-LPU26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ADQUISICION DE CONJUNTOS BOMBAS DE TIMON PARA UNIDADES DEPENDIENTES DE LA DVCB.</t>
+          <t>ADQUISICION DE MATERIALES DE CONSTRUCCION PARA LA HABILITACION DEL DEPARTAMENTO SANIDAD DEL DNRD</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>38/12 - Comando de la Flota de Mar</t>
+          <t>38/6 - INTENDENCIA NAVAL USHUAIA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>38/12 - Comando de la Flota de Mar</t>
+          <t>38/6 - INTENDENCIA NAVAL USHUAIA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1480,29 +1480,29 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>23/9/2026</t>
+          <t>24/9/2026</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>37/2-0092-LPU26</t>
+          <t>84/129-0684-LPU26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SERVICIO DE EXTRACCIÓN, TRASPORTE, MANTENIMIENTO Y LIMPIEZA RED CLOACAL DE LA GUARNICIÓN CENTINELA</t>
+          <t>ADQUISICIÓN DE MAQUINAS Y HERRAMIENTAS MENORES PARA VEHICULO BLINDADO M113</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>37/002 - Unidad Tecnica Administrativa Contable Digeapoyo</t>
+          <t>84/129 - Dirección de Arsenales</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>37/002 - Unidad Tecnica Administrativa Contable Digeapoyo</t>
+          <t>84/129 - Dirección de Arsenales</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1512,29 +1512,29 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>23/9/2026</t>
+          <t>24/9/2026</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>340/1-0056-LPU26</t>
+          <t>38/37-0474-LPU26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE COMBUSTIBLE RADA LA PLATA - SOSTÉN LOGÍSTICO ANTÁRTICO</t>
+          <t>ADQUISICION DE TOMOGRAFO DENTAL</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>340/001 - Dirección General de Administración - SSSLD</t>
+          <t>38/37 - Hospital Naval Puerto Belgrano</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>340/001 - Dirección General de Administración - SSSLD</t>
+          <t>38/37 - Hospital Naval Puerto Belgrano</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1544,29 +1544,29 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>23/9/2026</t>
+          <t>24/9/2026</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>84/129-0682-LPU26</t>
+          <t>84/77-0685-LPU26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE INSUMOS Y REPUESTOS PARA EL MANTENIMIENTO DE VEHÍCULOS DEL B ARS 604</t>
+          <t>ADQUISICION DE DRONES MICRO- DGCICD</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>84/129 - Dirección de Arsenales</t>
+          <t>84/77 - Departamento Contaduría y Finanzas (EMGE)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>84/129 - Dirección de Arsenales</t>
+          <t>84/77 - Departamento Contaduría y Finanzas (EMGE)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1576,29 +1576,29 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>23/9/2026</t>
+          <t>24/9/2026</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>84/77-0683-LPU26</t>
+          <t>38/15-0476-LPU26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Adquisición de repuestos destinados al mantenimiento preventivo y correctivo de vehículos Ford F-350</t>
+          <t>Obtención de conservas, panificados para los destinos en la IBBA (1er Trimestre 2027)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>84/77 - Departamento Contaduría y Finanzas (EMGE)</t>
+          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>84/77 - Departamento Contaduría y Finanzas (EMGE)</t>
+          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1608,29 +1608,29 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>23/9/2026</t>
+          <t>24/9/2026</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>38/1-0458-LPU26</t>
+          <t>38/12-0478-LPU26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Adquisición de OCHO (8) bombas inyectoras marca “L’Orange” para los motores principales .</t>
+          <t>ADQUISICION DE EQUIPOS INDIVIDUALES DE AIRE ACONDICIONADO PROA PARA EL DESTRUCTOR A.R.A "SARANDI"</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
+          <t>38/12 - Comando de la Flota de Mar</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
+          <t>38/12 - Comando de la Flota de Mar</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1640,29 +1640,29 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>24/9/2026</t>
+          <t>25/9/2026</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>38/15-0459-LPU26</t>
+          <t>84/22-0686-LPU26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Adquisición de cortes cárnicos, cerdo, filet de merluza, pollo y huevo fresco para IBUS.</t>
+          <t>ADQUIRIR UN SERVICIO DE INSPECCIÓN Y MANTENIMIENTO DE ASCENSORES PARA EL CDO BR MTE XII.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>84/22 - Comando de Brigada de Monte XII</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>84/22 - Comando de Brigada de Monte XII</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1672,29 +1672,29 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>24/9/2026</t>
+          <t>25/9/2026</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>38/15-0460-LPU26</t>
+          <t>38/12-0480-LPU26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Obtención de conservas, panificados y lácteos para los destinos con asiento en la IBMP 1º TRIM 2027</t>
+          <t>ADQUISICIÓN DE BOMBAS NEUMÁTICAS E HIDROLAVADORAS PARA UNIDADES DEL COMANDO DE LA FLOTA DE MAR</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>38/12 - Comando de la Flota de Mar</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>38/12 - Comando de la Flota de Mar</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1704,29 +1704,29 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>24/9/2026</t>
+          <t>27/9/2026</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>38/15-0461-LPU26</t>
+          <t>38/12-0481-LPU26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Adquisición de conservas, panificados y queso rallado para los destinos con asiento en IBUS.</t>
+          <t>ADQUISICIÓN DE REP. PARA MANTENIMIENTO DE MOTOR GENERADOR WARTSILA P/ UNIDADES DEPENDIENTES DE COFM</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>38/12 - Comando de la Flota de Mar</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>38/12 - Comando de la Flota de Mar</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1736,29 +1736,29 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>24/9/2026</t>
+          <t>28/9/2026</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>38/15-0462-LPU26</t>
+          <t>84/26-0687-LPU26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Adquisición de conservas y panificados para los destinos con asiento en IBPB - 1° TRIMESTRE 2027</t>
+          <t>ADQUISICIÓN DE EQUIPOS BIOMEDICOS PARA EL H GRL 601 - HMC.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>84/26 - Hospital Militar Central 601</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>84/26 - Hospital Militar Central 601</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1768,29 +1768,29 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>24/9/2026</t>
+          <t>28/9/2026</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>38/15-0463-LPU26</t>
+          <t>38/1-0484-LPU26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Adquisición de víveres secos y condimentos para los destinos con asiento en IBPB - 1° TRIMESTRE 2027</t>
+          <t>Adquisición de UN (1) kit de repuestos para motores diésel Sulzer.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1800,29 +1800,29 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>24/9/2026</t>
+          <t>28/9/2026</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>38/15-0464-LPU26</t>
+          <t>47-0006-LPU26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Obtención de lácteos y fiambre para los destinos con asiento en la IBBA (1er Trimestre 2027)</t>
+          <t>Adquisición de lubricantes para los buques de investigación pesquera del INIDEP</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>47 - Dpto. de Compras y Servicios- INIDEP</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>47 - Dpto. de Compras y Servicios- INIDEP</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1832,29 +1832,29 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>24/9/2026</t>
+          <t>28/9/2026</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>38/15-0465-LPU26</t>
+          <t>84/31-0689-LPU26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Adquirir víveres secos y condimentos para los destinos con asiento en la IBUS para el 1er trimestre</t>
+          <t>CONTRATAR EL SERVICIO DE REPARACIÓN PARA EL TECHO DEL NIVEL SECUNDARIO DEL LMGB.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>84/31 - Liceo Militar General Belgrano</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>84/31 - Liceo Militar General Belgrano</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1864,29 +1864,29 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>24/9/2026</t>
+          <t>29/9/2026</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>38/15-0468-LPU26</t>
+          <t>84/129-0690-LPU26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Obtención de víveres secos y condimentos (1er TRIMESTRE) para los destinos con asiento en IBBA</t>
+          <t>SERVICIO DE REPARACIÓN DE TECHO Y SISTEMA DE DESAGÜE DEL EDIFICIO Nº 84 DEL B ARS 602</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>84/129 - Dirección de Arsenales</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>84/129 - Dirección de Arsenales</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1896,29 +1896,29 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>24/9/2026</t>
+          <t>29/9/2026</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>38/15-0470-LPU26</t>
+          <t>494-0002-LPU26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Obtención de cortes cárnicos y huevos para los destinos con asiento en la IBBA (1er Trimestre 2027)</t>
+          <t>Adquisición insumos para el Laboratorio del BNDG</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>494 - Área de Compras y Contrataciones</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>494 - Área de Compras y Contrataciones</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1928,29 +1928,29 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>24/9/2026</t>
+          <t>29/9/2026</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>38/15-0471-LPU26</t>
+          <t>38/1-0486-LPU26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Adquisición de cortes cárnicos, cerdo, filet de merluza, pollo y huevo fresco para IBPB - 1° T 2027</t>
+          <t>Adquisición de palo santo en trozos de 300 mm</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1960,29 +1960,29 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>24/9/2026</t>
+          <t>30/9/2026</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>279-0002-LPU26</t>
+          <t>38/38-0488-LPU26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Contratación del servicio de limpieza, desinfección y sanitización para los edificios de la PSA</t>
+          <t>SERVICIO DE RECONSTITUCIÓN DE CITOSTÁTICOS, FÓRMULAS MAGISTRALES Y DISPENSACIÓN DE MEDICAMENTOS</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>279/000 - Departamento de Compras - PSA</t>
+          <t>38/38 - MINISTERIO DE DEFENSA - ARMADA ARGENTINA - HOSPITAL NAVAL BUENOS AIRES CIRUJANO MAYOR DOCTOR PEDRO MALLO</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>279/000 - Departamento de Compras - PSA</t>
+          <t>38/38 - MINISTERIO DE DEFENSA - ARMADA ARGENTINA - HOSPITAL NAVAL BUENOS AIRES CIRUJANO MAYOR DOCTOR PEDRO MALLO</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1992,29 +1992,29 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>24/9/2026</t>
+          <t>30/9/2026</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>38/15-0472-LPU26</t>
+          <t>84/13-0691-LPU26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Obtención de cortes cárnicos para los destinos con asiento en la IBMP (1er Trimestre 2027)</t>
+          <t>APST P/ LA PROV DE INSUM, SIEM, COND Y HENIFICADO DEL CULT DE ALFALFA 2027/29 - ECN</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>84/13 - Dirección de Remonta y Veterinaria</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>84/13 - Dirección de Remonta y Veterinaria</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2024,29 +2024,29 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>24/9/2026</t>
+          <t>30/9/2026</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>38/6-0473-LPU26</t>
+          <t>84/77-0694-LPU26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ADQUISICION DE MATERIALES DE CONSTRUCCION PARA LA HABILITACION DEL DEPARTAMENTO SANIDAD DEL DNRD</t>
+          <t>ADQUISICIÓN DE BATERÍAS RECARGABLES DESTINADAS A EQUIPOS ELECTRÓNICOS</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>38/6 - INTENDENCIA NAVAL USHUAIA</t>
+          <t>84/77 - Departamento Contaduría y Finanzas (EMGE)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>38/6 - INTENDENCIA NAVAL USHUAIA</t>
+          <t>84/77 - Departamento Contaduría y Finanzas (EMGE)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2056,29 +2056,29 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>24/9/2026</t>
+          <t>30/9/2026</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>84/129-0684-LPU26</t>
+          <t>68-0013-LPU26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE MAQUINAS Y HERRAMIENTAS MENORES PARA VEHICULO BLINDADO M113</t>
+          <t>Adquisición de equipos de laboratorio con destino al INEIA (ALCANZADO POR PROTOCOLO MERCOSUR)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>84/129 - Dirección de Arsenales</t>
+          <t>68/00 - Departamento de Administracion de Bienes - ANLIS</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>84/129 - Dirección de Arsenales</t>
+          <t>68/00 - Departamento de Administracion de Bienes - ANLIS</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2088,29 +2088,29 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>24/9/2026</t>
+          <t>1/10/2026</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>38/37-0474-LPU26</t>
+          <t>84/31-0695-LPU26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ADQUISICION DE TOMOGRAFO DENTAL</t>
+          <t>CONTRATAR EL SERVICIO DE REMODELACION DE BAÑOS DEL CUERPO DE CADETES DEL LMGB</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>38/37 - Hospital Naval Puerto Belgrano</t>
+          <t>84/31 - Liceo Militar General Belgrano</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>38/37 - Hospital Naval Puerto Belgrano</t>
+          <t>84/31 - Liceo Militar General Belgrano</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2120,29 +2120,29 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>24/9/2026</t>
+          <t>1/10/2026</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>38/15-0475-LPU26</t>
+          <t>84/136-0696-LPU26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Obtención de víveres secos y condimentos (1er TRIMESTRE 2027) para los destinos con asiento en IBMP</t>
+          <t>SERVICIO DE MANTENIMIENTO, REPARACION Y REFACCION DEL ANEXO 3 DEL CASINO DE SUBOFICIALES DEL CGMBA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>84/136 COMANDO GUARNICIÓN MILITAR BUENOS AIRES</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>84/136 COMANDO GUARNICIÓN MILITAR BUENOS AIRES</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2152,29 +2152,29 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>24/9/2026</t>
+          <t>1/10/2026</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>84/77-0685-LPU26</t>
+          <t>45-0004-LPU26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ADQUISICION DE DRONES MICRO- DGCICD</t>
+          <t>Renovación licenciamiento plataforma Qlik para la Superintendencia de Seguros de la Nación.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>84/77 - Departamento Contaduría y Finanzas (EMGE)</t>
+          <t>45 - Dirección General de Administración-SSN</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>84/77 - Departamento Contaduría y Finanzas (EMGE)</t>
+          <t>45 - Dirección General de Administración-SSN</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2184,29 +2184,29 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>24/9/2026</t>
+          <t>1/10/2026</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>38/15-0476-LPU26</t>
+          <t>84/3-0697-LPU26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Obtención de conservas, panificados para los destinos en la IBBA (1er Trimestre 2027)</t>
+          <t>SERVICIO DE DOSIMETRIA PARA EL HMCC PARA EL 4TO TRIMESTRE DEL AÑO 2026.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>84/03 - Comando de la 1ra División de Ejército</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>84/03 - Comando de la 1ra División de Ejército</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2216,29 +2216,29 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>24/9/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>38/15-0477-LPU26</t>
+          <t>38/12-0494-LPU26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Obtención de Frutas y Verduras 1er Trimestre 2027, para los destinos con asiento en IBBA</t>
+          <t>ADQ. DE EQUIPOS DE RADIOCOMUNICACIONES UHF/VHF PARA EL DESTRUCTOR A.R.A "SARANDÍ"</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>38/12 - Comando de la Flota de Mar</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>38/12 - Comando de la Flota de Mar</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2248,29 +2248,29 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>24/9/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>38/12-0478-LPU26</t>
+          <t>84/143-0698-LPU26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ADQUISICION DE EQUIPOS INDIVIDUALES DE AIRE ACONDICIONADO PROA PARA EL DESTRUCTOR A.R.A "SARANDI"</t>
+          <t>1ra etapa 27 Adquisición de Víveres Cárnicos - Jef Agr A Camp 601</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>38/12 - Comando de la Flota de Mar</t>
+          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>38/12 - Comando de la Flota de Mar</t>
+          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2280,29 +2280,29 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>25/9/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>38/12-0480-LPU26</t>
+          <t>84/143-0699-LPU26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE BOMBAS NEUMÁTICAS E HIDROLAVADORAS PARA UNIDADES DEL COMANDO DE LA FLOTA DE MAR</t>
+          <t>1ra etapa 27 Adquisición de Frutas, Verduras y Hortalizas - Jef Agr A Camp 601</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>38/12 - Comando de la Flota de Mar</t>
+          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>38/12 - Comando de la Flota de Mar</t>
+          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2312,29 +2312,29 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>27/9/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>38/12-0481-LPU26</t>
+          <t>84/143-0700-LPU26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE REP. PARA MANTENIMIENTO DE MOTOR GENERADOR WARTSILA P/ UNIDADES DEPENDIENTES DE COFM</t>
+          <t>1ra etapa 27 Adquisición de Productos Panificados - Jef Agr A Camp 601</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>38/12 - Comando de la Flota de Mar</t>
+          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>38/12 - Comando de la Flota de Mar</t>
+          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2344,29 +2344,29 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>28/9/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>84/26-0687-LPU26</t>
+          <t>84/143-0701-LPU26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE EQUIPOS BIOMEDICOS PARA EL H GRL 601 - HMC.</t>
+          <t>1ra etapa 27 Adquisición de Productos Avícolas - Jef Agr A Camp 601</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>84/26 - Hospital Militar Central 601</t>
+          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>84/26 - Hospital Militar Central 601</t>
+          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2376,29 +2376,29 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>28/9/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>38/1-0484-LPU26</t>
+          <t>84/143-0702-LPU26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Adquisición de UN (1) kit de repuestos para motores diésel Sulzer.</t>
+          <t>1ra etapa 27 Adquisición de Víveres Frescos - Jef Agr A Camp 601</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
+          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
+          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2408,29 +2408,29 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>28/9/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>47-0006-LPU26</t>
+          <t>84/143-0703-LPU26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Adquisición de lubricantes para los buques de investigación pesquera del INIDEP</t>
+          <t>1ra etapa 27 Adquisición de Víveres Secos - Jef Agr A Camp 601</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>47 - Dpto. de Compras y Servicios- INIDEP</t>
+          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>47 - Dpto. de Compras y Servicios- INIDEP</t>
+          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2440,19 +2440,19 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>28/9/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>84/31-0689-LPU26</t>
+          <t>84/31-0704-LPU26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CONTRATAR EL SERVICIO DE REPARACIÓN PARA EL TECHO DEL NIVEL SECUNDARIO DEL LMGB.</t>
+          <t>ADQUISICION DE PRODUCTOS CARNICOS PARA RACIONAMIENTO DE CADETES DEL LMGB - 1er SEMESTRE 2027</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2472,29 +2472,29 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>29/9/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>84/129-0690-LPU26</t>
+          <t>84/31-0705-LPU26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SERVICIO DE REPARACIÓN DE TECHO Y SISTEMA DE DESAGÜE DEL EDIFICIO Nº 84 DEL B ARS 602</t>
+          <t>ADQUISICION DE FRUTAS Y VERDURAS PARA RACIONAMIENTO DE CADETES DEL LMGB - 1er SEMESTRE 2027</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>84/129 - Dirección de Arsenales</t>
+          <t>84/31 - Liceo Militar General Belgrano</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>84/129 - Dirección de Arsenales</t>
+          <t>84/31 - Liceo Militar General Belgrano</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2504,29 +2504,29 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>29/9/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>494-0002-LPU26</t>
+          <t>84/31-0706-LPU26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Adquisición insumos para el Laboratorio del BNDG</t>
+          <t>ADQUISICION DE PRODUCTOS AVICOLAS PARA RACIONAMIENTO DE CADETES DEL LMGB - 1er SEMESTRE 2027</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>494 - Área de Compras y Contrataciones</t>
+          <t>84/31 - Liceo Militar General Belgrano</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>494 - Área de Compras y Contrataciones</t>
+          <t>84/31 - Liceo Militar General Belgrano</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2536,29 +2536,29 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>29/9/2026</t>
+          <t>5/10/2026</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>38/1-0486-LPU26</t>
+          <t>84/31-0707-LPU26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Adquisición de palo santo en trozos de 300 mm</t>
+          <t>ADQUISICION DE VIVERES FRESCOS PARA RACIONAMIENTO DE CADETES DEL LMGB - 1er SEMESTRE 2027</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
+          <t>84/31 - Liceo Militar General Belgrano</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
+          <t>84/31 - Liceo Militar General Belgrano</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2568,29 +2568,29 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>30/9/2026</t>
+          <t>5/10/2026</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>38/38-0488-LPU26</t>
+          <t>84/31-0708-LPU26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SERVICIO DE RECONSTITUCIÓN DE CITOSTÁTICOS, FÓRMULAS MAGISTRALES Y DISPENSACIÓN DE MEDICAMENTOS</t>
+          <t>ADQUISICION DE VIVERES SECOS PARA RACIONAMIENTO DE CADETES DEL LMGB - 1er SEMESTRE 2027</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>38/38 - MINISTERIO DE DEFENSA - ARMADA ARGENTINA - HOSPITAL NAVAL BUENOS AIRES CIRUJANO MAYOR DOCTOR PEDRO MALLO</t>
+          <t>84/31 - Liceo Militar General Belgrano</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>38/38 - MINISTERIO DE DEFENSA - ARMADA ARGENTINA - HOSPITAL NAVAL BUENOS AIRES CIRUJANO MAYOR DOCTOR PEDRO MALLO</t>
+          <t>84/31 - Liceo Militar General Belgrano</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2600,29 +2600,29 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>30/9/2026</t>
+          <t>5/10/2026</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>84/13-0691-LPU26</t>
+          <t>84/31-0709-LPU26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>APST P/ LA PROV DE INSUM, SIEM, COND Y HENIFICADO DEL CULT DE ALFALFA 2027/29 - ECN</t>
+          <t>ADQUISICION DE PRODUCTOS DE PANIFICACION PARA RACIONAMIENTO DE CADETES DEL LMGB - 1er SEMESTRE 2027</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>84/13 - Dirección de Remonta y Veterinaria</t>
+          <t>84/31 - Liceo Militar General Belgrano</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>84/13 - Dirección de Remonta y Veterinaria</t>
+          <t>84/31 - Liceo Militar General Belgrano</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2632,29 +2632,29 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>30/9/2026</t>
+          <t>5/10/2026</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>84/77-0694-LPU26</t>
+          <t>39-0040-LPU26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE BATERÍAS RECARGABLES DESTINADAS A EQUIPOS ELECTRÓNICOS</t>
+          <t>SERVICIO DE MANTENIMIENTO CORRECTIVO DE LOS SISTEMAS DE VIDEO DE LA PREFECTURA NAVAL ARGENTINA.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>84/77 - Departamento Contaduría y Finanzas (EMGE)</t>
+          <t>39 - Dirección General de Administración- PNA</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>84/77 - Departamento Contaduría y Finanzas (EMGE)</t>
+          <t>39 - Dirección General de Administración- PNA</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2664,29 +2664,29 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>30/9/2026</t>
+          <t>5/10/2026</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>68-0013-LPU26</t>
+          <t>38/1-0499-LPU26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Adquisición de equipos de laboratorio con destino al INEIA (ALCANZADO POR PROTOCOLO MERCOSUR)</t>
+          <t>Adq. de UN (1) lote de repuestos de motor diésel MTU 396 6V TC 52 .</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>68/00 - Departamento de Administracion de Bienes - ANLIS</t>
+          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>68/00 - Departamento de Administracion de Bienes - ANLIS</t>
+          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2696,29 +2696,29 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1/10/2026</t>
+          <t>5/10/2026</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>84/31-0695-LPU26</t>
+          <t>39-0041-LPU26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CONTRATAR EL SERVICIO DE REMODELACION DE BAÑOS DEL CUERPO DE CADETES DEL LMGB</t>
+          <t>ADQUISICIÓN DE REPUESTOS PARA MOTORES MARINOS GM DETROIT DIESEL PARA GC TIPO 48 Y STAND TENDER.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>84/31 - Liceo Militar General Belgrano</t>
+          <t>39 - Dirección General de Administración- PNA</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>84/31 - Liceo Militar General Belgrano</t>
+          <t>39 - Dirección General de Administración- PNA</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2728,29 +2728,29 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1/10/2026</t>
+          <t>5/10/2026</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>84/136-0696-LPU26</t>
+          <t>84/13-0712-LPU26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENIMIENTO, REPARACION Y REFACCION DEL ANEXO 3 DEL CASINO DE SUBOFICIALES DEL CGMBA</t>
+          <t>APST P LA PROV DE ALFALFA CAMPAÑA 2027/39 341has - ECN</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>84/136 COMANDO GUARNICIÓN MILITAR BUENOS AIRES</t>
+          <t>84/13 - Dirección de Remonta y Veterinaria</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>84/136 COMANDO GUARNICIÓN MILITAR BUENOS AIRES</t>
+          <t>84/13 - Dirección de Remonta y Veterinaria</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2760,29 +2760,29 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1/10/2026</t>
+          <t>5/10/2026</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>38/12-0494-LPU26</t>
+          <t>84/13-0713-LPU26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ADQ. DE EQUIPOS DE RADIOCOMUNICACIONES UHF/VHF PARA EL DESTRUCTOR A.R.A "SARANDÍ"</t>
+          <t>APST P LA PROV DE ALFALFA CAMPAÑA 2027/39 91has - ECN</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>38/12 - Comando de la Flota de Mar</t>
+          <t>84/13 - Dirección de Remonta y Veterinaria</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>38/12 - Comando de la Flota de Mar</t>
+          <t>84/13 - Dirección de Remonta y Veterinaria</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2792,29 +2792,29 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>6/10/2026</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>84/143-0698-LPU26</t>
+          <t>84/129-0724-LPU26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1ra etapa 27 Adquisición de Víveres Cárnicos - Jef Agr A Camp 601</t>
+          <t>ADQUISICIÓN DE FRENTES Y CONJUNTOS DE TABLEROS DE INSTRUMENTOS PARA VEHÍCULOS DE COMBATE TAM 2C</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
+          <t>84/129 - Dirección de Arsenales</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
+          <t>84/129 - Dirección de Arsenales</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2824,29 +2824,29 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>7/10/2026</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>84/143-0699-LPU26</t>
+          <t>43-0007-LPU26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1ra etapa 27 Adquisición de Frutas, Verduras y Hortalizas - Jef Agr A Camp 601</t>
+          <t>Recambio de controladoras NetApp FAS8700 bajo la modalidad TECH REFRESH..</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
+          <t>43 - Departamento de Compras - Instituto de Ayuda Financiera para pago de Retiros y Pensiones Militares - Ministerio de Defensa</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
+          <t>43 - Departamento de Compras - Instituto de Ayuda Financiera para pago de Retiros y Pensiones Militares - Ministerio de Defensa</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2856,29 +2856,29 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>8/10/2026</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>84/143-0700-LPU26</t>
+          <t>84/129-0725-LPU26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1ra etapa 27 Adquisición de Productos Panificados - Jef Agr A Camp 601</t>
+          <t>SERVICIOS DE CATERING PARA RELEVOS DE AUTORIDADES, CEREMONIAS PATRIAS Y RECEPCIÓN DE DELEGACIONES</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
+          <t>84/129 - Dirección de Arsenales</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
+          <t>84/129 - Dirección de Arsenales</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2888,29 +2888,29 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>8/10/2026</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>84/143-0701-LPU26</t>
+          <t>38/37-0504-LPU26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1ra etapa 27 Adquisición de Productos Avícolas - Jef Agr A Camp 601</t>
+          <t>AMPOLLAS HEPARINIZANTES</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
+          <t>38/37 - Hospital Naval Puerto Belgrano</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
+          <t>38/37 - Hospital Naval Puerto Belgrano</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2920,29 +2920,29 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>8/10/2026</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>84/143-0702-LPU26</t>
+          <t>84/129-0728-LPU26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1ra etapa 27 Adquisición de Víveres Frescos - Jef Agr A Camp 601</t>
+          <t>ADQUISICIÓN DE RUEDAS DE APOYO PARA SISTEMA DE RODAMIENTO DE VEHÍCULOS DE COMBATE TAM 2C</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
+          <t>84/129 - Dirección de Arsenales</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
+          <t>84/129 - Dirección de Arsenales</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2952,29 +2952,29 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>8/10/2026</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>84/143-0703-LPU26</t>
+          <t>84/129-0729-LPU26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1ra etapa 27 Adquisición de Víveres Secos - Jef Agr A Camp 601</t>
+          <t>ADQUISICIÓN KIT DE FRENOS PARA RODAMIENTO PARA CAÑONES 155 MM</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
+          <t>84/129 - Dirección de Arsenales</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
+          <t>84/129 - Dirección de Arsenales</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2984,29 +2984,29 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>8/10/2026</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>84/31-0704-LPU26</t>
+          <t>39-0042-LPU26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ADQUISICION DE PRODUCTOS CARNICOS PARA RACIONAMIENTO DE CADETES DEL LMGB - 1er SEMESTRE 2027</t>
+          <t>RECONVERSIÓN MODULAR DE UNA (1) AERONAVE AIRBUS HELICOPTERS AS365 DAUPHIN, N2 AL ESTÁNDAR AS365 N3+.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>84/31 - Liceo Militar General Belgrano</t>
+          <t>39 - Dirección General de Administración- PNA</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>84/31 - Liceo Militar General Belgrano</t>
+          <t>39 - Dirección General de Administración- PNA</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3016,29 +3016,29 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>9/10/2026</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>84/31-0705-LPU26</t>
+          <t>38/25-0506-LPU26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ADQUISICION DE FRUTAS Y VERDURAS PARA RACIONAMIENTO DE CADETES DEL LMGB - 1er SEMESTRE 2027</t>
+          <t>Adquisición de un kit de controles de vuelo, transmisión y rotor de cola con prestación de soporte.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>84/31 - Liceo Militar General Belgrano</t>
+          <t>38/25 - Base Aeronaval Comandante espora</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>84/31 - Liceo Militar General Belgrano</t>
+          <t>38/25 - Base Aeronaval Comandante espora</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3048,29 +3048,29 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>9/10/2026</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>84/31-0706-LPU26</t>
+          <t>38/25-0508-LPU26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ADQUISICION DE PRODUCTOS AVICOLAS PARA RACIONAMIENTO DE CADETES DEL LMGB - 1er SEMESTRE 2027</t>
+          <t>Provisión de un kit de sistemas de fluido y mangueras aeronáuticas.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>84/31 - Liceo Militar General Belgrano</t>
+          <t>38/25 - Base Aeronaval Comandante espora</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>84/31 - Liceo Militar General Belgrano</t>
+          <t>38/25 - Base Aeronaval Comandante espora</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3080,29 +3080,29 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>5/10/2026</t>
+          <t>9/10/2026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>84/31-0707-LPU26</t>
+          <t>38/25-0509-LPU26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ADQUISICION DE VIVERES FRESCOS PARA RACIONAMIENTO DE CADETES DEL LMGB - 1er SEMESTRE 2027</t>
+          <t>Adquisición de un kit de cabina, transparencias y accesos, con prestación de soporte técnico.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>84/31 - Liceo Militar General Belgrano</t>
+          <t>38/25 - Base Aeronaval Comandante espora</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>84/31 - Liceo Militar General Belgrano</t>
+          <t>38/25 - Base Aeronaval Comandante espora</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3112,29 +3112,29 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>5/10/2026</t>
+          <t>9/10/2026</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>84/31-0708-LPU26</t>
+          <t>38/25-0510-LPU26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ADQUISICION DE VIVERES SECOS PARA RACIONAMIENTO DE CADETES DEL LMGB - 1er SEMESTRE 2027</t>
+          <t>Adquisición de un kit de estructura, tren de aterrizaje e interfaz de motor</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>84/31 - Liceo Militar General Belgrano</t>
+          <t>38/25 - Base Aeronaval Comandante espora</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>84/31 - Liceo Militar General Belgrano</t>
+          <t>38/25 - Base Aeronaval Comandante espora</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3144,29 +3144,29 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>5/10/2026</t>
+          <t>9/10/2026</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>84/31-0709-LPU26</t>
+          <t>30-0015-LPU26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ADQUISICION DE PRODUCTOS DE PANIFICACION PARA RACIONAMIENTO DE CADETES DEL LMGB - 1er SEMESTRE 2027</t>
+          <t>Adquisición de aerosoles orgánicos OC, Granadas CS, Granadas de humo blanco y sonoro lumínicas</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>84/31 - Liceo Militar General Belgrano</t>
+          <t>30/00 - División Contrataciones - Policia Federal Argentina</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>84/31 - Liceo Militar General Belgrano</t>
+          <t>30/00 - División Contrataciones - Policia Federal Argentina</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3176,29 +3176,29 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>5/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>39-0040-LPU26</t>
+          <t>38/37-0513-LPU26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENIMIENTO CORRECTIVO DE LOS SISTEMAS DE VIDEO DE LA PREFECTURA NAVAL ARGENTINA.</t>
+          <t>CONTRATACION DEL SERVICIO DE GUARDIA DE ANESTESIA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>39 - Dirección General de Administración- PNA</t>
+          <t>38/37 - Hospital Naval Puerto Belgrano</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>39 - Dirección General de Administración- PNA</t>
+          <t>38/37 - Hospital Naval Puerto Belgrano</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3208,29 +3208,29 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>5/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>39-0041-LPU26</t>
+          <t>38/37-0514-LPU26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE REPUESTOS PARA MOTORES MARINOS GM DETROIT DIESEL PARA GC TIPO 48 Y STAND TENDER.</t>
+          <t>PROVISION CONTINUA DE MODULOS PARA INTERVENCIONES QUIRURGICAS</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>39 - Dirección General de Administración- PNA</t>
+          <t>38/37 - Hospital Naval Puerto Belgrano</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>39 - Dirección General de Administración- PNA</t>
+          <t>38/37 - Hospital Naval Puerto Belgrano</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3240,29 +3240,29 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>5/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>84/13-0712-LPU26</t>
+          <t>38/37-0517-LPU26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>APST P LA PROV DE ALFALFA CAMPAÑA 2027/39 341has - ECN</t>
+          <t>PROVISON CONTINUA DE SERVICIOS MEDICOS ASISTENCIALES EN GUARDIAS MEDICAS</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>84/13 - Dirección de Remonta y Veterinaria</t>
+          <t>38/37 - Hospital Naval Puerto Belgrano</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>84/13 - Dirección de Remonta y Veterinaria</t>
+          <t>38/37 - Hospital Naval Puerto Belgrano</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3272,29 +3272,29 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>5/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>84/13-0713-LPU26</t>
+          <t>38/1-0521-LPU26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>APST P LA PROV DE ALFALFA CAMPAÑA 2027/39 91has - ECN</t>
+          <t>ADQ. DE DOCE (12) LOTES DE REPUESTOS PARA SISTEMAS DE INYECCIÓN DE MOTORES DIÉSEL MTU 396 6V TC 52</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>84/13 - Dirección de Remonta y Veterinaria</t>
+          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>84/13 - Dirección de Remonta y Veterinaria</t>
+          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3304,29 +3304,29 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>6/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>84/129-0724-LPU26</t>
+          <t>38/1-0522-LPU26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE FRENTES Y CONJUNTOS DE TABLEROS DE INSTRUMENTOS PARA VEHÍCULOS DE COMBATE TAM 2C</t>
+          <t>Adquisición de TRES (3) Enfriadores de Agua de Mar para Motor Generador MTU 396 TC 52-12 V</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>84/129 - Dirección de Arsenales</t>
+          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>84/129 - Dirección de Arsenales</t>
+          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3336,29 +3336,29 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>7/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>39-0042-LPU26</t>
+          <t>38/1-0523-LPU26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>RECONVERSIÓN MODULAR DE UNA (1) AERONAVE AIRBUS HELICOPTERS AS365 DAUPHIN, N2 AL ESTÁNDAR AS365 N3+.</t>
+          <t>ADQ. DE LOTE DE REPUESTOS PARA MANTENIMIENTO MAYOR DE 16.000 HS MOTOR GENERADOR WARTSILA.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>39 - Dirección General de Administración- PNA</t>
+          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>39 - Dirección General de Administración- PNA</t>
+          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3368,29 +3368,29 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>9/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>38/25-0506-LPU26</t>
+          <t>38/27-0524-LPU26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Adquisición de un kit de controles de vuelo, transmisión y rotor de cola con prestación de soporte.</t>
+          <t>ADQUISICIÓN DE EQUIPAMENTO ÓPTICO-ELECTRÓNICO MULTIFUNCIÓN PARA UNITAS 2027</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>38/25 - Base Aeronaval Comandante espora</t>
+          <t>38/27 - Agrupación Servicios de Cuartel</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>38/25 - Base Aeronaval Comandante espora</t>
+          <t>38/27 - Agrupación Servicios de Cuartel</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3400,29 +3400,29 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>9/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>38/25-0508-LPU26</t>
+          <t>38/27-0525-LPU26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Provisión de un kit de sistemas de fluido y mangueras aeronáuticas.</t>
+          <t>ADQUISICIÓN DE EQUIPOS PORTÁTILES DE VISIÓN NOCTURNA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>38/25 - Base Aeronaval Comandante espora</t>
+          <t>38/27 - Agrupación Servicios de Cuartel</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>38/25 - Base Aeronaval Comandante espora</t>
+          <t>38/27 - Agrupación Servicios de Cuartel</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3432,29 +3432,29 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>9/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>38/25-0509-LPU26</t>
+          <t>38/1-0526-LPU26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Adquisición de un kit de cabina, transparencias y accesos, con prestación de soporte técnico.</t>
+          <t>Prestación del serv. de prep. de sup. mediante hidrojetting y pintado en Destructor ARA SARANDI</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>38/25 - Base Aeronaval Comandante espora</t>
+          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>38/25 - Base Aeronaval Comandante espora</t>
+          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3464,29 +3464,29 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>9/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>38/25-0510-LPU26</t>
+          <t>38/27-0529-LPU26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Adquisición de un kit de estructura, tren de aterrizaje e interfaz de motor</t>
+          <t>ADQUISICIÓN DE EQUIPOS PORTÁTILES DE OBSERVACIÓN TÉRMICA E INFRARROJA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>38/25 - Base Aeronaval Comandante espora</t>
+          <t>38/27 - Agrupación Servicios de Cuartel</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>38/25 - Base Aeronaval Comandante espora</t>
+          <t>38/27 - Agrupación Servicios de Cuartel</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3496,39 +3496,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>9/10/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>30-0015-LPU26</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Adquisición de aerosoles orgánicos OC, Granadas CS, Granadas de humo blanco y sonoro lumínicas</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>30/00 - División Contrataciones - Policia Federal Argentina</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>30/00 - División Contrataciones - Policia Federal Argentina</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Publicado</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>10/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
     </row>

--- a/procesos_armada.xlsx
+++ b/procesos_armada.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F96"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,22 +463,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>92-0006-LPU26</t>
+          <t>68-0011-LPU26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DIGITALIZACIÓN DEL ARCHIVO DE PUBLICACIONES PERIÓDICAS DE LA EDITORIAL SARMIENTO</t>
+          <t>Contratación del Servicio de limpieza edilicia -INE (Alcanzado por el Protocolo del Mercosur)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>92 - Departamento de Compras y Contrataciones- BN</t>
+          <t>68/00 - Departamento de Administracion de Bienes - ANLIS</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>92 - Departamento de Compras y Contrataciones- BN</t>
+          <t>68/00 - Departamento de Administracion de Bienes - ANLIS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -488,29 +488,29 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>16/9/2026</t>
+          <t>17/9/2026</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>68-0010-LPU26</t>
+          <t>78-0010-LPU26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SERVICIO DE SEGURIDAD Y VIGILANCIA EN CAMPO DE INMUNIZACIONES MARCOS PAZ - INPB</t>
+          <t>Adquisición de sobres para ensobrado manual de pasaportes y DNI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>68/00 - Departamento de Administracion de Bienes - ANLIS</t>
+          <t>78/000 - División Compras</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>68/00 - Departamento de Administracion de Bienes - ANLIS</t>
+          <t>78/000 - División Compras</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -520,29 +520,29 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>16/9/2026</t>
+          <t>17/9/2026</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>315-0014-LPU26</t>
+          <t>347-0028-LPU26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Servicio de provisión e instalación de 1100 metros cuadrados (m2) de piso de goma</t>
+          <t>CONTRATACIÓN DE MANO DE OBRA ESPECIALIZADA Y ADQUISICIÓN DE REPUESTOS PARA EL HELICOPTERO AW169</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>315/000 - Dirección General de Administración - MP</t>
+          <t>347/000 - Dirección General de Administración - MS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>315/000 - Dirección General de Administración - MP</t>
+          <t>347/000 - Dirección General de Administración - MS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -552,29 +552,29 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>16/9/2026</t>
+          <t>17/9/2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>21-0023-LPU26</t>
+          <t>78-0011-LPU26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENIMIENTO EQUIPOS DE AIRE ACONDICIONADO EN LA SEDE CENTRAL Y AMBA DE LA DNM.-</t>
+          <t>Contratación del servicio de mantenimiento, reparación e instalación de aires acondicionados.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21/000 - Dirección General de Administración - DNM</t>
+          <t>78/000 - División Compras</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>21/000 - Dirección General de Administración - DNM</t>
+          <t>78/000 - División Compras</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -584,29 +584,29 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>16/9/2026</t>
+          <t>17/9/2026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>47-0005-LPU26</t>
+          <t>79/8-0006-LPU26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Contratación seguro para los buques de investigación pesquera del INIDEP</t>
+          <t>Servicio integral llave en mano Ceremonia de los Best Tourism Villages de ONU Turismo 2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>47 - Dpto. de Compras y Servicios- INIDEP</t>
+          <t>79/8 - SAF322 - SECRETARIA DE AMBIENTE Y TURISMO</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>47 - Dpto. de Compras y Servicios- INIDEP</t>
+          <t>79/8 - SAF322 - SECRETARIA DE AMBIENTE Y TURISMO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -616,29 +616,29 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>16/9/2026</t>
+          <t>18/9/2026</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>52-0044-LPU26</t>
+          <t>38/3-0443-LPU26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN DE UN (1) SERVICIO PROFESIONAL PARA ACTUALIZACIÓN Y EVOLUCIÓN FUNCIONAL SISTEMA SIGCER</t>
+          <t>CONCESIÓN ONEROSA DEL SERVICIO DE BUFFET Y CANTINA DEL CLUB GOLF DE PUERTO BELGRANO (BNPB)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52 - Coordinación de Compras y Contrataciones - SENASA</t>
+          <t>38/03 - UOC de la Intendencia Naval Puerto Belgrano - Armada Argentina</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>52 - Coordinación de Compras y Contrataciones - SENASA</t>
+          <t>38/03 - UOC de la Intendencia Naval Puerto Belgrano - Armada Argentina</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -648,29 +648,29 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>16/9/2026</t>
+          <t>18/9/2026</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>64-0019-LPU26</t>
+          <t>340/1-0054-LPU26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Adquisición de Computadoras de Escritorio tipo AIO y Monitores para la S.R.T.</t>
+          <t>ADQUISICIÓN DE REPUESTOS DE BASE - SOSTÉN LOGÍSTICO ANTÁRTICO.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>64/000 - Departamento de Compras y Contrataciones- SRT</t>
+          <t>340/001 - Dirección General de Administración - SSSLD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>64/000 - Departamento de Compras y Contrataciones- SRT</t>
+          <t>340/001 - Dirección General de Administración - SSSLD</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -680,29 +680,29 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>16/9/2026</t>
+          <t>18/9/2026</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>38/3-0440-LPU26</t>
+          <t>38/19-0445-LPU26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CONCESIÓN ONEROSA DEL SERVICIO DE BUFFET Y CANTINA DEL ESTADIO DE DEPORTES DE LA BNPB.</t>
+          <t>DGED ADQUISICIÓN DE DOS SIMULADORES DE TIRO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>38/03 - UOC de la Intendencia Naval Puerto Belgrano - Armada Argentina</t>
+          <t>38/19 - División Contrataciones del Cuartel General del EMGA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>38/03 - UOC de la Intendencia Naval Puerto Belgrano - Armada Argentina</t>
+          <t>38/19 - División Contrataciones del Cuartel General del EMGA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -712,29 +712,29 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>16/9/2026</t>
+          <t>21/9/2026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>68-0011-LPU26</t>
+          <t>84/24-0677-LPU26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Contratación del Servicio de limpieza edilicia -INE (Alcanzado por el Protocolo del Mercosur)</t>
+          <t>ALQUILER DE EQUIPOS DE FOTOCOPIADO DIGITAL E IMPRESORAS, SU MANTENIMIENTO INTEGRAL E INSUMOS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>68/00 - Departamento de Administracion de Bienes - ANLIS</t>
+          <t>84/24 - Colegio Militar de la Nación - Compras y Contrataciones</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>68/00 - Departamento de Administracion de Bienes - ANLIS</t>
+          <t>84/24 - Colegio Militar de la Nación - Compras y Contrataciones</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -744,29 +744,29 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17/9/2026</t>
+          <t>21/9/2026</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>78-0010-LPU26</t>
+          <t>38/6-0447-LPU26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Adquisición de sobres para ensobrado manual de pasaportes y DNI</t>
+          <t>RECAMBIO Y READECUACION INTEGRAL DEL SISTEMA DE CALEFACCION DEL EDIFICIO COMANDO DEL BIM4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>78/000 - División Compras</t>
+          <t>38/6 - INTENDENCIA NAVAL USHUAIA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>78/000 - División Compras</t>
+          <t>38/6 - INTENDENCIA NAVAL USHUAIA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17/9/2026</t>
+          <t>21/9/2026</t>
         </is>
       </c>
     </row>
@@ -815,22 +815,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347-0028-LPU26</t>
+          <t>39-0039-LPU26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CONTRATACIÓN DE MANO DE OBRA ESPECIALIZADA Y ADQUISICIÓN DE REPUESTOS PARA EL HELICOPTERO AW169</t>
+          <t>REPARACIÓN INTEGRAL DEL GUARDACOSTAS PNA GC-65 “MARTÍN GARCIA”.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>347/000 - Dirección General de Administración - MS</t>
+          <t>39 - Dirección General de Administración- PNA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>347/000 - Dirección General de Administración - MS</t>
+          <t>39 - Dirección General de Administración- PNA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -840,29 +840,29 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>17/9/2026</t>
+          <t>22/9/2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>78-0011-LPU26</t>
+          <t>68-0012-LPU26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Contratación del servicio de mantenimiento, reparación e instalación de aires acondicionados.</t>
+          <t>INSTALACION DE ALAMBRADO Y DEFORESTACIÓN EN CAMPO ANEXO - INPB (ALCANZADO POR PROTOCOLO MERCOSUR)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>78/000 - División Compras</t>
+          <t>68/00 - Departamento de Administracion de Bienes - ANLIS</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>78/000 - División Compras</t>
+          <t>68/00 - Departamento de Administracion de Bienes - ANLIS</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -872,29 +872,29 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>17/9/2026</t>
+          <t>22/9/2026</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>79/8-0006-LPU26</t>
+          <t>38/12-0453-LPU26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Servicio integral llave en mano Ceremonia de los Best Tourism Villages de ONU Turismo 2026</t>
+          <t>ADQUISICION DE CONJUNTOS BOMBAS DE TIMON PARA UNIDADES DEPENDIENTES DE LA DVCB.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>79/8 - SAF322 - SECRETARIA DE AMBIENTE Y TURISMO</t>
+          <t>38/12 - Comando de la Flota de Mar</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>79/8 - SAF322 - SECRETARIA DE AMBIENTE Y TURISMO</t>
+          <t>38/12 - Comando de la Flota de Mar</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -904,29 +904,29 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>18/9/2026</t>
+          <t>23/9/2026</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>38/3-0443-LPU26</t>
+          <t>37/2-0092-LPU26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CONCESIÓN ONEROSA DEL SERVICIO DE BUFFET Y CANTINA DEL CLUB GOLF DE PUERTO BELGRANO (BNPB)</t>
+          <t>SERVICIO DE EXTRACCIÓN, TRASPORTE, MANTENIMIENTO Y LIMPIEZA RED CLOACAL DE LA GUARNICIÓN CENTINELA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>38/03 - UOC de la Intendencia Naval Puerto Belgrano - Armada Argentina</t>
+          <t>37/002 - Unidad Tecnica Administrativa Contable Digeapoyo</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>38/03 - UOC de la Intendencia Naval Puerto Belgrano - Armada Argentina</t>
+          <t>37/002 - Unidad Tecnica Administrativa Contable Digeapoyo</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -936,19 +936,19 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>18/9/2026</t>
+          <t>23/9/2026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>340/1-0054-LPU26</t>
+          <t>340/1-0056-LPU26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE REPUESTOS DE BASE - SOSTÉN LOGÍSTICO ANTÁRTICO.</t>
+          <t>ADQUISICIÓN DE COMBUSTIBLE RADA LA PLATA - SOSTÉN LOGÍSTICO ANTÁRTICO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -968,29 +968,29 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>18/9/2026</t>
+          <t>23/9/2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>38/19-0445-LPU26</t>
+          <t>38/15-0462-LPU26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DGED ADQUISICIÓN DE DOS SIMULADORES DE TIRO</t>
+          <t>Adquisición de conservas y panificados para los destinos con asiento en IBPB - 1° TRIMESTRE 2027</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>38/19 - División Contrataciones del Cuartel General del EMGA</t>
+          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>38/19 - División Contrataciones del Cuartel General del EMGA</t>
+          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1000,29 +1000,29 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>21/9/2026</t>
+          <t>24/9/2026</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>84/24-0677-LPU26</t>
+          <t>38/15-0463-LPU26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ALQUILER DE EQUIPOS DE FOTOCOPIADO DIGITAL E IMPRESORAS, SU MANTENIMIENTO INTEGRAL E INSUMOS</t>
+          <t>Adquisición de víveres secos y condimentos para los destinos con asiento en IBPB - 1° TRIMESTRE 2027</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>84/24 - Colegio Militar de la Nación - Compras y Contrataciones</t>
+          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>84/24 - Colegio Militar de la Nación - Compras y Contrataciones</t>
+          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1032,29 +1032,29 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>21/9/2026</t>
+          <t>24/9/2026</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>38/6-0447-LPU26</t>
+          <t>38/15-0464-LPU26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RECAMBIO Y READECUACION INTEGRAL DEL SISTEMA DE CALEFACCION DEL EDIFICIO COMANDO DEL BIM4</t>
+          <t>Obtención de lácteos y fiambre para los destinos con asiento en la IBBA (1er Trimestre 2027)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>38/6 - INTENDENCIA NAVAL USHUAIA</t>
+          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>38/6 - INTENDENCIA NAVAL USHUAIA</t>
+          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1064,29 +1064,29 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>21/9/2026</t>
+          <t>24/9/2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>39-0039-LPU26</t>
+          <t>38/15-0468-LPU26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>REPARACIÓN INTEGRAL DEL GUARDACOSTAS PNA GC-65 “MARTÍN GARCIA”.</t>
+          <t>Obtención de víveres secos y condimentos (1er TRIMESTRE) para los destinos con asiento en IBBA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>39 - Dirección General de Administración- PNA</t>
+          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>39 - Dirección General de Administración- PNA</t>
+          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1096,29 +1096,29 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>22/9/2026</t>
+          <t>24/9/2026</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>68-0012-LPU26</t>
+          <t>38/4-0469-LPU26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>INSTALACION DE ALAMBRADO Y DEFORESTACIÓN EN CAMPO ANEXO - INPB (ALCANZADO POR PROTOCOLO MERCOSUR)</t>
+          <t>SERVICIO DE REPARACIÓN E IMPERMEABILIZACIÓN DE LOS TECHOS DEL ARSENAL NAVAL MAR DEL PLATA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>68/00 - Departamento de Administracion de Bienes - ANLIS</t>
+          <t>38/4 - INTENDENCIA NAVAL MAR DEL PLATA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>68/00 - Departamento de Administracion de Bienes - ANLIS</t>
+          <t>38/4 - INTENDENCIA NAVAL MAR DEL PLATA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1128,29 +1128,29 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>22/9/2026</t>
+          <t>24/9/2026</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>38/12-0453-LPU26</t>
+          <t>38/15-0470-LPU26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ADQUISICION DE CONJUNTOS BOMBAS DE TIMON PARA UNIDADES DEPENDIENTES DE LA DVCB.</t>
+          <t>Obtención de cortes cárnicos y huevos para los destinos con asiento en la IBBA (1er Trimestre 2027)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>38/12 - Comando de la Flota de Mar</t>
+          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>38/12 - Comando de la Flota de Mar</t>
+          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1160,29 +1160,29 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>23/9/2026</t>
+          <t>24/9/2026</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>37/2-0092-LPU26</t>
+          <t>38/15-0471-LPU26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SERVICIO DE EXTRACCIÓN, TRASPORTE, MANTENIMIENTO Y LIMPIEZA RED CLOACAL DE LA GUARNICIÓN CENTINELA</t>
+          <t>Adquisición de cortes cárnicos, cerdo, filet de merluza, pollo y huevo fresco para IBPB - 1° T 2027</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>37/002 - Unidad Tecnica Administrativa Contable Digeapoyo</t>
+          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>37/002 - Unidad Tecnica Administrativa Contable Digeapoyo</t>
+          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1192,29 +1192,29 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>23/9/2026</t>
+          <t>24/9/2026</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>340/1-0056-LPU26</t>
+          <t>38/6-0473-LPU26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE COMBUSTIBLE RADA LA PLATA - SOSTÉN LOGÍSTICO ANTÁRTICO</t>
+          <t>ADQUISICION DE MATERIALES DE CONSTRUCCION PARA LA HABILITACION DEL DEPARTAMENTO SANIDAD DEL DNRD</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>340/001 - Dirección General de Administración - SSSLD</t>
+          <t>38/6 - INTENDENCIA NAVAL USHUAIA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>340/001 - Dirección General de Administración - SSSLD</t>
+          <t>38/6 - INTENDENCIA NAVAL USHUAIA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1224,29 +1224,29 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>23/9/2026</t>
+          <t>24/9/2026</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>38/15-0462-LPU26</t>
+          <t>84/129-0684-LPU26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Adquisición de conservas y panificados para los destinos con asiento en IBPB - 1° TRIMESTRE 2027</t>
+          <t>ADQUISICIÓN DE MAQUINAS Y HERRAMIENTAS MENORES PARA VEHICULO BLINDADO M113</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>84/129 - Dirección de Arsenales</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>84/129 - Dirección de Arsenales</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1263,22 +1263,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>38/15-0463-LPU26</t>
+          <t>38/37-0474-LPU26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Adquisición de víveres secos y condimentos para los destinos con asiento en IBPB - 1° TRIMESTRE 2027</t>
+          <t>ADQUISICION DE TOMOGRAFO DENTAL</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>38/37 - Hospital Naval Puerto Belgrano</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>38/37 - Hospital Naval Puerto Belgrano</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1295,22 +1295,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>38/15-0464-LPU26</t>
+          <t>84/77-0685-LPU26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Obtención de lácteos y fiambre para los destinos con asiento en la IBBA (1er Trimestre 2027)</t>
+          <t>ADQUISICION DE DRONES MICRO- DGCICD</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>84/77 - Departamento Contaduría y Finanzas (EMGE)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>84/77 - Departamento Contaduría y Finanzas (EMGE)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1327,12 +1327,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>38/15-0468-LPU26</t>
+          <t>38/15-0476-LPU26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Obtención de víveres secos y condimentos (1er TRIMESTRE) para los destinos con asiento en IBBA</t>
+          <t>Obtención de conservas, panificados para los destinos en la IBBA (1er Trimestre 2027)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1359,22 +1359,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>38/4-0469-LPU26</t>
+          <t>38/12-0478-LPU26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SERVICIO DE REPARACIÓN E IMPERMEABILIZACIÓN DE LOS TECHOS DEL ARSENAL NAVAL MAR DEL PLATA</t>
+          <t>ADQUISICION DE EQUIPOS INDIVIDUALES DE AIRE ACONDICIONADO PROA PARA EL DESTRUCTOR A.R.A "SARANDI"</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>38/4 - INTENDENCIA NAVAL MAR DEL PLATA</t>
+          <t>38/12 - Comando de la Flota de Mar</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>38/4 - INTENDENCIA NAVAL MAR DEL PLATA</t>
+          <t>38/12 - Comando de la Flota de Mar</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1384,29 +1384,29 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>24/9/2026</t>
+          <t>25/9/2026</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>38/15-0470-LPU26</t>
+          <t>84/22-0686-LPU26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Obtención de cortes cárnicos y huevos para los destinos con asiento en la IBBA (1er Trimestre 2027)</t>
+          <t>ADQUIRIR UN SERVICIO DE INSPECCIÓN Y MANTENIMIENTO DE ASCENSORES PARA EL CDO BR MTE XII.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>84/22 - Comando de Brigada de Monte XII</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>84/22 - Comando de Brigada de Monte XII</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1416,29 +1416,29 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>24/9/2026</t>
+          <t>25/9/2026</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>38/15-0471-LPU26</t>
+          <t>38/12-0480-LPU26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Adquisición de cortes cárnicos, cerdo, filet de merluza, pollo y huevo fresco para IBPB - 1° T 2027</t>
+          <t>ADQUISICIÓN DE BOMBAS NEUMÁTICAS E HIDROLAVADORAS PARA UNIDADES DEL COMANDO DE LA FLOTA DE MAR</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>38/12 - Comando de la Flota de Mar</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>38/12 - Comando de la Flota de Mar</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1448,29 +1448,29 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>24/9/2026</t>
+          <t>27/9/2026</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>38/6-0473-LPU26</t>
+          <t>38/12-0481-LPU26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ADQUISICION DE MATERIALES DE CONSTRUCCION PARA LA HABILITACION DEL DEPARTAMENTO SANIDAD DEL DNRD</t>
+          <t>ADQUISICIÓN DE REP. PARA MANTENIMIENTO DE MOTOR GENERADOR WARTSILA P/ UNIDADES DEPENDIENTES DE COFM</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>38/6 - INTENDENCIA NAVAL USHUAIA</t>
+          <t>38/12 - Comando de la Flota de Mar</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>38/6 - INTENDENCIA NAVAL USHUAIA</t>
+          <t>38/12 - Comando de la Flota de Mar</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1480,29 +1480,29 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>24/9/2026</t>
+          <t>28/9/2026</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>84/129-0684-LPU26</t>
+          <t>84/26-0687-LPU26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE MAQUINAS Y HERRAMIENTAS MENORES PARA VEHICULO BLINDADO M113</t>
+          <t>ADQUISICIÓN DE EQUIPOS BIOMEDICOS PARA EL H GRL 601 - HMC.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>84/129 - Dirección de Arsenales</t>
+          <t>84/26 - Hospital Militar Central 601</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>84/129 - Dirección de Arsenales</t>
+          <t>84/26 - Hospital Militar Central 601</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1512,29 +1512,29 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>24/9/2026</t>
+          <t>28/9/2026</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>38/37-0474-LPU26</t>
+          <t>38/1-0484-LPU26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ADQUISICION DE TOMOGRAFO DENTAL</t>
+          <t>Adquisición de UN (1) kit de repuestos para motores diésel Sulzer.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>38/37 - Hospital Naval Puerto Belgrano</t>
+          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>38/37 - Hospital Naval Puerto Belgrano</t>
+          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1544,29 +1544,29 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>24/9/2026</t>
+          <t>28/9/2026</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>84/77-0685-LPU26</t>
+          <t>47-0006-LPU26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ADQUISICION DE DRONES MICRO- DGCICD</t>
+          <t>Adquisición de lubricantes para los buques de investigación pesquera del INIDEP</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>84/77 - Departamento Contaduría y Finanzas (EMGE)</t>
+          <t>47 - Dpto. de Compras y Servicios- INIDEP</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>84/77 - Departamento Contaduría y Finanzas (EMGE)</t>
+          <t>47 - Dpto. de Compras y Servicios- INIDEP</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1576,29 +1576,29 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>24/9/2026</t>
+          <t>28/9/2026</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>38/15-0476-LPU26</t>
+          <t>84/31-0689-LPU26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Obtención de conservas, panificados para los destinos en la IBBA (1er Trimestre 2027)</t>
+          <t>CONTRATAR EL SERVICIO DE REPARACIÓN PARA EL TECHO DEL NIVEL SECUNDARIO DEL LMGB.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>84/31 - Liceo Militar General Belgrano</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>38/15 JEFATURA DE OBTENCION DE LA ARMADA</t>
+          <t>84/31 - Liceo Militar General Belgrano</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1608,29 +1608,29 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>24/9/2026</t>
+          <t>29/9/2026</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>38/12-0478-LPU26</t>
+          <t>84/129-0690-LPU26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ADQUISICION DE EQUIPOS INDIVIDUALES DE AIRE ACONDICIONADO PROA PARA EL DESTRUCTOR A.R.A "SARANDI"</t>
+          <t>SERVICIO DE REPARACIÓN DE TECHO Y SISTEMA DE DESAGÜE DEL EDIFICIO Nº 84 DEL B ARS 602</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>38/12 - Comando de la Flota de Mar</t>
+          <t>84/129 - Dirección de Arsenales</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>38/12 - Comando de la Flota de Mar</t>
+          <t>84/129 - Dirección de Arsenales</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1640,29 +1640,29 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>25/9/2026</t>
+          <t>29/9/2026</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>84/22-0686-LPU26</t>
+          <t>494-0002-LPU26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ADQUIRIR UN SERVICIO DE INSPECCIÓN Y MANTENIMIENTO DE ASCENSORES PARA EL CDO BR MTE XII.</t>
+          <t>Adquisición insumos para el Laboratorio del BNDG</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>84/22 - Comando de Brigada de Monte XII</t>
+          <t>494 - Área de Compras y Contrataciones</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>84/22 - Comando de Brigada de Monte XII</t>
+          <t>494 - Área de Compras y Contrataciones</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1672,29 +1672,29 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>25/9/2026</t>
+          <t>29/9/2026</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>38/12-0480-LPU26</t>
+          <t>38/1-0486-LPU26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE BOMBAS NEUMÁTICAS E HIDROLAVADORAS PARA UNIDADES DEL COMANDO DE LA FLOTA DE MAR</t>
+          <t>Adquisición de palo santo en trozos de 300 mm</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>38/12 - Comando de la Flota de Mar</t>
+          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>38/12 - Comando de la Flota de Mar</t>
+          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1704,29 +1704,29 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>27/9/2026</t>
+          <t>30/9/2026</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>38/12-0481-LPU26</t>
+          <t>38/38-0488-LPU26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE REP. PARA MANTENIMIENTO DE MOTOR GENERADOR WARTSILA P/ UNIDADES DEPENDIENTES DE COFM</t>
+          <t>SERVICIO DE RECONSTITUCIÓN DE CITOSTÁTICOS, FÓRMULAS MAGISTRALES Y DISPENSACIÓN DE MEDICAMENTOS</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>38/12 - Comando de la Flota de Mar</t>
+          <t>38/38 - MINISTERIO DE DEFENSA - ARMADA ARGENTINA - HOSPITAL NAVAL BUENOS AIRES CIRUJANO MAYOR DOCTOR PEDRO MALLO</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>38/12 - Comando de la Flota de Mar</t>
+          <t>38/38 - MINISTERIO DE DEFENSA - ARMADA ARGENTINA - HOSPITAL NAVAL BUENOS AIRES CIRUJANO MAYOR DOCTOR PEDRO MALLO</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1736,29 +1736,29 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>28/9/2026</t>
+          <t>30/9/2026</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>84/26-0687-LPU26</t>
+          <t>84/13-0691-LPU26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE EQUIPOS BIOMEDICOS PARA EL H GRL 601 - HMC.</t>
+          <t>APST P/ LA PROV DE INSUM, SIEM, COND Y HENIFICADO DEL CULT DE ALFALFA 2027/29 - ECN</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>84/26 - Hospital Militar Central 601</t>
+          <t>84/13 - Dirección de Remonta y Veterinaria</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>84/26 - Hospital Militar Central 601</t>
+          <t>84/13 - Dirección de Remonta y Veterinaria</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1768,29 +1768,29 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>28/9/2026</t>
+          <t>30/9/2026</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>38/1-0484-LPU26</t>
+          <t>84/77-0694-LPU26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Adquisición de UN (1) kit de repuestos para motores diésel Sulzer.</t>
+          <t>ADQUISICIÓN DE BATERÍAS RECARGABLES DESTINADAS A EQUIPOS ELECTRÓNICOS</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
+          <t>84/77 - Departamento Contaduría y Finanzas (EMGE)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
+          <t>84/77 - Departamento Contaduría y Finanzas (EMGE)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1800,29 +1800,29 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>28/9/2026</t>
+          <t>30/9/2026</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>47-0006-LPU26</t>
+          <t>68-0013-LPU26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Adquisición de lubricantes para los buques de investigación pesquera del INIDEP</t>
+          <t>Adquisición de equipos de laboratorio con destino al INEIA (ALCANZADO POR PROTOCOLO MERCOSUR)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>47 - Dpto. de Compras y Servicios- INIDEP</t>
+          <t>68/00 - Departamento de Administracion de Bienes - ANLIS</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>47 - Dpto. de Compras y Servicios- INIDEP</t>
+          <t>68/00 - Departamento de Administracion de Bienes - ANLIS</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1832,19 +1832,19 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>28/9/2026</t>
+          <t>1/10/2026</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>84/31-0689-LPU26</t>
+          <t>84/31-0695-LPU26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CONTRATAR EL SERVICIO DE REPARACIÓN PARA EL TECHO DEL NIVEL SECUNDARIO DEL LMGB.</t>
+          <t>CONTRATAR EL SERVICIO DE REMODELACION DE BAÑOS DEL CUERPO DE CADETES DEL LMGB</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1864,29 +1864,29 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>29/9/2026</t>
+          <t>1/10/2026</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>84/129-0690-LPU26</t>
+          <t>84/136-0696-LPU26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SERVICIO DE REPARACIÓN DE TECHO Y SISTEMA DE DESAGÜE DEL EDIFICIO Nº 84 DEL B ARS 602</t>
+          <t>SERVICIO DE MANTENIMIENTO, REPARACION Y REFACCION DEL ANEXO 3 DEL CASINO DE SUBOFICIALES DEL CGMBA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>84/129 - Dirección de Arsenales</t>
+          <t>84/136 COMANDO GUARNICIÓN MILITAR BUENOS AIRES</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>84/129 - Dirección de Arsenales</t>
+          <t>84/136 COMANDO GUARNICIÓN MILITAR BUENOS AIRES</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1896,29 +1896,29 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>29/9/2026</t>
+          <t>1/10/2026</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>494-0002-LPU26</t>
+          <t>45-0004-LPU26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Adquisición insumos para el Laboratorio del BNDG</t>
+          <t>Renovación licenciamiento plataforma Qlik para la Superintendencia de Seguros de la Nación.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>494 - Área de Compras y Contrataciones</t>
+          <t>45 - Dirección General de Administración-SSN</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>494 - Área de Compras y Contrataciones</t>
+          <t>45 - Dirección General de Administración-SSN</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1928,29 +1928,29 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>29/9/2026</t>
+          <t>1/10/2026</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>38/1-0486-LPU26</t>
+          <t>84/3-0697-LPU26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Adquisición de palo santo en trozos de 300 mm</t>
+          <t>SERVICIO DE DOSIMETRIA PARA EL HMCC PARA EL 4TO TRIMESTRE DEL AÑO 2026.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
+          <t>84/03 - Comando de la 1ra División de Ejército</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
+          <t>84/03 - Comando de la 1ra División de Ejército</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1960,29 +1960,29 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>30/9/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>38/38-0488-LPU26</t>
+          <t>38/12-0494-LPU26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SERVICIO DE RECONSTITUCIÓN DE CITOSTÁTICOS, FÓRMULAS MAGISTRALES Y DISPENSACIÓN DE MEDICAMENTOS</t>
+          <t>ADQ. DE EQUIPOS DE RADIOCOMUNICACIONES UHF/VHF PARA EL DESTRUCTOR A.R.A "SARANDÍ"</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>38/38 - MINISTERIO DE DEFENSA - ARMADA ARGENTINA - HOSPITAL NAVAL BUENOS AIRES CIRUJANO MAYOR DOCTOR PEDRO MALLO</t>
+          <t>38/12 - Comando de la Flota de Mar</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>38/38 - MINISTERIO DE DEFENSA - ARMADA ARGENTINA - HOSPITAL NAVAL BUENOS AIRES CIRUJANO MAYOR DOCTOR PEDRO MALLO</t>
+          <t>38/12 - Comando de la Flota de Mar</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1992,29 +1992,29 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>30/9/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>84/13-0691-LPU26</t>
+          <t>84/143-0698-LPU26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>APST P/ LA PROV DE INSUM, SIEM, COND Y HENIFICADO DEL CULT DE ALFALFA 2027/29 - ECN</t>
+          <t>1ra etapa 27 Adquisición de Víveres Cárnicos - Jef Agr A Camp 601</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>84/13 - Dirección de Remonta y Veterinaria</t>
+          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>84/13 - Dirección de Remonta y Veterinaria</t>
+          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2024,29 +2024,29 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>30/9/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>84/77-0694-LPU26</t>
+          <t>84/143-0699-LPU26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE BATERÍAS RECARGABLES DESTINADAS A EQUIPOS ELECTRÓNICOS</t>
+          <t>1ra etapa 27 Adquisición de Frutas, Verduras y Hortalizas - Jef Agr A Camp 601</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>84/77 - Departamento Contaduría y Finanzas (EMGE)</t>
+          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>84/77 - Departamento Contaduría y Finanzas (EMGE)</t>
+          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2056,29 +2056,29 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>30/9/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>68-0013-LPU26</t>
+          <t>84/143-0700-LPU26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Adquisición de equipos de laboratorio con destino al INEIA (ALCANZADO POR PROTOCOLO MERCOSUR)</t>
+          <t>1ra etapa 27 Adquisición de Productos Panificados - Jef Agr A Camp 601</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>68/00 - Departamento de Administracion de Bienes - ANLIS</t>
+          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>68/00 - Departamento de Administracion de Bienes - ANLIS</t>
+          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2088,29 +2088,29 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1/10/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>84/31-0695-LPU26</t>
+          <t>84/143-0701-LPU26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CONTRATAR EL SERVICIO DE REMODELACION DE BAÑOS DEL CUERPO DE CADETES DEL LMGB</t>
+          <t>1ra etapa 27 Adquisición de Productos Avícolas - Jef Agr A Camp 601</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>84/31 - Liceo Militar General Belgrano</t>
+          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>84/31 - Liceo Militar General Belgrano</t>
+          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2120,29 +2120,29 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1/10/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>84/136-0696-LPU26</t>
+          <t>84/143-0702-LPU26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENIMIENTO, REPARACION Y REFACCION DEL ANEXO 3 DEL CASINO DE SUBOFICIALES DEL CGMBA</t>
+          <t>1ra etapa 27 Adquisición de Víveres Frescos - Jef Agr A Camp 601</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>84/136 COMANDO GUARNICIÓN MILITAR BUENOS AIRES</t>
+          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>84/136 COMANDO GUARNICIÓN MILITAR BUENOS AIRES</t>
+          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2152,29 +2152,29 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1/10/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>45-0004-LPU26</t>
+          <t>84/143-0703-LPU26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Renovación licenciamiento plataforma Qlik para la Superintendencia de Seguros de la Nación.</t>
+          <t>1ra etapa 27 Adquisición de Víveres Secos - Jef Agr A Camp 601</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>45 - Dirección General de Administración-SSN</t>
+          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>45 - Dirección General de Administración-SSN</t>
+          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2184,29 +2184,29 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1/10/2026</t>
+          <t>2/10/2026</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>84/3-0697-LPU26</t>
+          <t>84/31-0704-LPU26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SERVICIO DE DOSIMETRIA PARA EL HMCC PARA EL 4TO TRIMESTRE DEL AÑO 2026.</t>
+          <t>ADQUISICION DE PRODUCTOS CARNICOS PARA RACIONAMIENTO DE CADETES DEL LMGB - 1er SEMESTRE 2027</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>84/03 - Comando de la 1ra División de Ejército</t>
+          <t>84/31 - Liceo Militar General Belgrano</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>84/03 - Comando de la 1ra División de Ejército</t>
+          <t>84/31 - Liceo Militar General Belgrano</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2223,22 +2223,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>38/12-0494-LPU26</t>
+          <t>84/31-0705-LPU26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ADQ. DE EQUIPOS DE RADIOCOMUNICACIONES UHF/VHF PARA EL DESTRUCTOR A.R.A "SARANDÍ"</t>
+          <t>ADQUISICION DE FRUTAS Y VERDURAS PARA RACIONAMIENTO DE CADETES DEL LMGB - 1er SEMESTRE 2027</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>38/12 - Comando de la Flota de Mar</t>
+          <t>84/31 - Liceo Militar General Belgrano</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>38/12 - Comando de la Flota de Mar</t>
+          <t>84/31 - Liceo Militar General Belgrano</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2255,22 +2255,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>84/143-0698-LPU26</t>
+          <t>84/31-0706-LPU26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1ra etapa 27 Adquisición de Víveres Cárnicos - Jef Agr A Camp 601</t>
+          <t>ADQUISICION DE PRODUCTOS AVICOLAS PARA RACIONAMIENTO DE CADETES DEL LMGB - 1er SEMESTRE 2027</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
+          <t>84/31 - Liceo Militar General Belgrano</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
+          <t>84/31 - Liceo Militar General Belgrano</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2280,29 +2280,29 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>5/10/2026</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>84/143-0699-LPU26</t>
+          <t>84/31-0707-LPU26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1ra etapa 27 Adquisición de Frutas, Verduras y Hortalizas - Jef Agr A Camp 601</t>
+          <t>ADQUISICION DE VIVERES FRESCOS PARA RACIONAMIENTO DE CADETES DEL LMGB - 1er SEMESTRE 2027</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
+          <t>84/31 - Liceo Militar General Belgrano</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
+          <t>84/31 - Liceo Militar General Belgrano</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2312,29 +2312,29 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>5/10/2026</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>84/143-0700-LPU26</t>
+          <t>84/31-0708-LPU26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1ra etapa 27 Adquisición de Productos Panificados - Jef Agr A Camp 601</t>
+          <t>ADQUISICION DE VIVERES SECOS PARA RACIONAMIENTO DE CADETES DEL LMGB - 1er SEMESTRE 2027</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
+          <t>84/31 - Liceo Militar General Belgrano</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
+          <t>84/31 - Liceo Militar General Belgrano</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2344,29 +2344,29 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>5/10/2026</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>84/143-0701-LPU26</t>
+          <t>84/31-0709-LPU26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1ra etapa 27 Adquisición de Productos Avícolas - Jef Agr A Camp 601</t>
+          <t>ADQUISICION DE PRODUCTOS DE PANIFICACION PARA RACIONAMIENTO DE CADETES DEL LMGB - 1er SEMESTRE 2027</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
+          <t>84/31 - Liceo Militar General Belgrano</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
+          <t>84/31 - Liceo Militar General Belgrano</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2376,29 +2376,29 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>5/10/2026</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>84/143-0702-LPU26</t>
+          <t>39-0040-LPU26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1ra etapa 27 Adquisición de Víveres Frescos - Jef Agr A Camp 601</t>
+          <t>SERVICIO DE MANTENIMIENTO CORRECTIVO DE LOS SISTEMAS DE VIDEO DE LA PREFECTURA NAVAL ARGENTINA.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
+          <t>39 - Dirección General de Administración- PNA</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
+          <t>39 - Dirección General de Administración- PNA</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2408,29 +2408,29 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>5/10/2026</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>84/143-0703-LPU26</t>
+          <t>38/1-0499-LPU26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1ra etapa 27 Adquisición de Víveres Secos - Jef Agr A Camp 601</t>
+          <t>Adq. de UN (1) lote de repuestos de motor diésel MTU 396 6V TC 52 .</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
+          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>84/143-JEFATURA DE AGRUPACION DE ARTILLERIA DE CAMPAÑA 601</t>
+          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2440,29 +2440,29 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>5/10/2026</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>84/31-0704-LPU26</t>
+          <t>39-0041-LPU26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ADQUISICION DE PRODUCTOS CARNICOS PARA RACIONAMIENTO DE CADETES DEL LMGB - 1er SEMESTRE 2027</t>
+          <t>ADQUISICIÓN DE REPUESTOS PARA MOTORES MARINOS GM DETROIT DIESEL PARA GC TIPO 48 Y STAND TENDER.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>84/31 - Liceo Militar General Belgrano</t>
+          <t>39 - Dirección General de Administración- PNA</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>84/31 - Liceo Militar General Belgrano</t>
+          <t>39 - Dirección General de Administración- PNA</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2472,29 +2472,29 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>5/10/2026</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>84/31-0705-LPU26</t>
+          <t>84/13-0712-LPU26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ADQUISICION DE FRUTAS Y VERDURAS PARA RACIONAMIENTO DE CADETES DEL LMGB - 1er SEMESTRE 2027</t>
+          <t>APST P LA PROV DE ALFALFA CAMPAÑA 2027/39 341has - ECN</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>84/31 - Liceo Militar General Belgrano</t>
+          <t>84/13 - Dirección de Remonta y Veterinaria</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>84/31 - Liceo Militar General Belgrano</t>
+          <t>84/13 - Dirección de Remonta y Veterinaria</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2504,29 +2504,29 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2/10/2026</t>
+          <t>5/10/2026</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>84/31-0706-LPU26</t>
+          <t>84/13-0713-LPU26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ADQUISICION DE PRODUCTOS AVICOLAS PARA RACIONAMIENTO DE CADETES DEL LMGB - 1er SEMESTRE 2027</t>
+          <t>APST P LA PROV DE ALFALFA CAMPAÑA 2027/39 91has - ECN</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>84/31 - Liceo Militar General Belgrano</t>
+          <t>84/13 - Dirección de Remonta y Veterinaria</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>84/31 - Liceo Militar General Belgrano</t>
+          <t>84/13 - Dirección de Remonta y Veterinaria</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2536,29 +2536,29 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>5/10/2026</t>
+          <t>6/10/2026</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>84/31-0707-LPU26</t>
+          <t>84/129-0724-LPU26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ADQUISICION DE VIVERES FRESCOS PARA RACIONAMIENTO DE CADETES DEL LMGB - 1er SEMESTRE 2027</t>
+          <t>ADQUISICIÓN DE FRENTES Y CONJUNTOS DE TABLEROS DE INSTRUMENTOS PARA VEHÍCULOS DE COMBATE TAM 2C</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>84/31 - Liceo Militar General Belgrano</t>
+          <t>84/129 - Dirección de Arsenales</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>84/31 - Liceo Militar General Belgrano</t>
+          <t>84/129 - Dirección de Arsenales</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2568,29 +2568,29 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>5/10/2026</t>
+          <t>7/10/2026</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>84/31-0708-LPU26</t>
+          <t>43-0007-LPU26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ADQUISICION DE VIVERES SECOS PARA RACIONAMIENTO DE CADETES DEL LMGB - 1er SEMESTRE 2027</t>
+          <t>Recambio de controladoras NetApp FAS8700 bajo la modalidad TECH REFRESH..</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>84/31 - Liceo Militar General Belgrano</t>
+          <t>43 - Departamento de Compras - Instituto de Ayuda Financiera para pago de Retiros y Pensiones Militares - Ministerio de Defensa</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>84/31 - Liceo Militar General Belgrano</t>
+          <t>43 - Departamento de Compras - Instituto de Ayuda Financiera para pago de Retiros y Pensiones Militares - Ministerio de Defensa</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2600,29 +2600,29 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>5/10/2026</t>
+          <t>8/10/2026</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>84/31-0709-LPU26</t>
+          <t>84/129-0725-LPU26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ADQUISICION DE PRODUCTOS DE PANIFICACION PARA RACIONAMIENTO DE CADETES DEL LMGB - 1er SEMESTRE 2027</t>
+          <t>SERVICIOS DE CATERING PARA RELEVOS DE AUTORIDADES, CEREMONIAS PATRIAS Y RECEPCIÓN DE DELEGACIONES</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>84/31 - Liceo Militar General Belgrano</t>
+          <t>84/129 - Dirección de Arsenales</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>84/31 - Liceo Militar General Belgrano</t>
+          <t>84/129 - Dirección de Arsenales</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2632,29 +2632,29 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>5/10/2026</t>
+          <t>8/10/2026</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>39-0040-LPU26</t>
+          <t>38/37-0504-LPU26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENIMIENTO CORRECTIVO DE LOS SISTEMAS DE VIDEO DE LA PREFECTURA NAVAL ARGENTINA.</t>
+          <t>AMPOLLAS HEPARINIZANTES</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>39 - Dirección General de Administración- PNA</t>
+          <t>38/37 - Hospital Naval Puerto Belgrano</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>39 - Dirección General de Administración- PNA</t>
+          <t>38/37 - Hospital Naval Puerto Belgrano</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2664,29 +2664,29 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>5/10/2026</t>
+          <t>8/10/2026</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>38/1-0499-LPU26</t>
+          <t>84/129-0728-LPU26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Adq. de UN (1) lote de repuestos de motor diésel MTU 396 6V TC 52 .</t>
+          <t>ADQUISICIÓN DE RUEDAS DE APOYO PARA SISTEMA DE RODAMIENTO DE VEHÍCULOS DE COMBATE TAM 2C</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
+          <t>84/129 - Dirección de Arsenales</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
+          <t>84/129 - Dirección de Arsenales</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2696,29 +2696,29 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>5/10/2026</t>
+          <t>8/10/2026</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>39-0041-LPU26</t>
+          <t>84/129-0729-LPU26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE REPUESTOS PARA MOTORES MARINOS GM DETROIT DIESEL PARA GC TIPO 48 Y STAND TENDER.</t>
+          <t>ADQUISICIÓN KIT DE FRENOS PARA RODAMIENTO PARA CAÑONES 155 MM</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>39 - Dirección General de Administración- PNA</t>
+          <t>84/129 - Dirección de Arsenales</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>39 - Dirección General de Administración- PNA</t>
+          <t>84/129 - Dirección de Arsenales</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2728,29 +2728,29 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>5/10/2026</t>
+          <t>8/10/2026</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>84/13-0712-LPU26</t>
+          <t>39-0042-LPU26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>APST P LA PROV DE ALFALFA CAMPAÑA 2027/39 341has - ECN</t>
+          <t>RECONVERSIÓN MODULAR DE UNA (1) AERONAVE AIRBUS HELICOPTERS AS365 DAUPHIN, N2 AL ESTÁNDAR AS365 N3+.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>84/13 - Dirección de Remonta y Veterinaria</t>
+          <t>39 - Dirección General de Administración- PNA</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>84/13 - Dirección de Remonta y Veterinaria</t>
+          <t>39 - Dirección General de Administración- PNA</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2760,29 +2760,29 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>5/10/2026</t>
+          <t>9/10/2026</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>84/13-0713-LPU26</t>
+          <t>38/25-0506-LPU26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>APST P LA PROV DE ALFALFA CAMPAÑA 2027/39 91has - ECN</t>
+          <t>Adquisición de un kit de controles de vuelo, transmisión y rotor de cola con prestación de soporte.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>84/13 - Dirección de Remonta y Veterinaria</t>
+          <t>38/25 - Base Aeronaval Comandante espora</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>84/13 - Dirección de Remonta y Veterinaria</t>
+          <t>38/25 - Base Aeronaval Comandante espora</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2792,29 +2792,29 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>6/10/2026</t>
+          <t>9/10/2026</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>84/129-0724-LPU26</t>
+          <t>38/25-0508-LPU26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE FRENTES Y CONJUNTOS DE TABLEROS DE INSTRUMENTOS PARA VEHÍCULOS DE COMBATE TAM 2C</t>
+          <t>Provisión de un kit de sistemas de fluido y mangueras aeronáuticas.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>84/129 - Dirección de Arsenales</t>
+          <t>38/25 - Base Aeronaval Comandante espora</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>84/129 - Dirección de Arsenales</t>
+          <t>38/25 - Base Aeronaval Comandante espora</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2824,29 +2824,29 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>7/10/2026</t>
+          <t>9/10/2026</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>43-0007-LPU26</t>
+          <t>38/25-0509-LPU26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Recambio de controladoras NetApp FAS8700 bajo la modalidad TECH REFRESH..</t>
+          <t>Adquisición de un kit de cabina, transparencias y accesos, con prestación de soporte técnico.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>43 - Departamento de Compras - Instituto de Ayuda Financiera para pago de Retiros y Pensiones Militares - Ministerio de Defensa</t>
+          <t>38/25 - Base Aeronaval Comandante espora</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>43 - Departamento de Compras - Instituto de Ayuda Financiera para pago de Retiros y Pensiones Militares - Ministerio de Defensa</t>
+          <t>38/25 - Base Aeronaval Comandante espora</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2856,29 +2856,29 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>8/10/2026</t>
+          <t>9/10/2026</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>84/129-0725-LPU26</t>
+          <t>38/25-0510-LPU26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SERVICIOS DE CATERING PARA RELEVOS DE AUTORIDADES, CEREMONIAS PATRIAS Y RECEPCIÓN DE DELEGACIONES</t>
+          <t>Adquisición de un kit de estructura, tren de aterrizaje e interfaz de motor</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>84/129 - Dirección de Arsenales</t>
+          <t>38/25 - Base Aeronaval Comandante espora</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>84/129 - Dirección de Arsenales</t>
+          <t>38/25 - Base Aeronaval Comandante espora</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2888,29 +2888,29 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>8/10/2026</t>
+          <t>9/10/2026</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>38/37-0504-LPU26</t>
+          <t>30-0015-LPU26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>AMPOLLAS HEPARINIZANTES</t>
+          <t>Adquisición de aerosoles orgánicos OC, Granadas CS, Granadas de humo blanco y sonoro lumínicas</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>38/37 - Hospital Naval Puerto Belgrano</t>
+          <t>30/00 - División Contrataciones - Policia Federal Argentina</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>38/37 - Hospital Naval Puerto Belgrano</t>
+          <t>30/00 - División Contrataciones - Policia Federal Argentina</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2920,29 +2920,29 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>8/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>84/129-0728-LPU26</t>
+          <t>38/37-0513-LPU26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE RUEDAS DE APOYO PARA SISTEMA DE RODAMIENTO DE VEHÍCULOS DE COMBATE TAM 2C</t>
+          <t>CONTRATACION DEL SERVICIO DE GUARDIA DE ANESTESIA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>84/129 - Dirección de Arsenales</t>
+          <t>38/37 - Hospital Naval Puerto Belgrano</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>84/129 - Dirección de Arsenales</t>
+          <t>38/37 - Hospital Naval Puerto Belgrano</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2952,29 +2952,29 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>8/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>84/129-0729-LPU26</t>
+          <t>38/37-0514-LPU26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN KIT DE FRENOS PARA RODAMIENTO PARA CAÑONES 155 MM</t>
+          <t>PROVISION CONTINUA DE MODULOS PARA INTERVENCIONES QUIRURGICAS</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>84/129 - Dirección de Arsenales</t>
+          <t>38/37 - Hospital Naval Puerto Belgrano</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>84/129 - Dirección de Arsenales</t>
+          <t>38/37 - Hospital Naval Puerto Belgrano</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2984,29 +2984,29 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>8/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>39-0042-LPU26</t>
+          <t>38/37-0517-LPU26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>RECONVERSIÓN MODULAR DE UNA (1) AERONAVE AIRBUS HELICOPTERS AS365 DAUPHIN, N2 AL ESTÁNDAR AS365 N3+.</t>
+          <t>PROVISON CONTINUA DE SERVICIOS MEDICOS ASISTENCIALES EN GUARDIAS MEDICAS</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>39 - Dirección General de Administración- PNA</t>
+          <t>38/37 - Hospital Naval Puerto Belgrano</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>39 - Dirección General de Administración- PNA</t>
+          <t>38/37 - Hospital Naval Puerto Belgrano</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3016,29 +3016,29 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>9/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>38/25-0506-LPU26</t>
+          <t>38/1-0521-LPU26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Adquisición de un kit de controles de vuelo, transmisión y rotor de cola con prestación de soporte.</t>
+          <t>ADQ. DE DOCE (12) LOTES DE REPUESTOS PARA SISTEMAS DE INYECCIÓN DE MOTORES DIÉSEL MTU 396 6V TC 52</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>38/25 - Base Aeronaval Comandante espora</t>
+          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>38/25 - Base Aeronaval Comandante espora</t>
+          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3048,29 +3048,29 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>9/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>38/25-0508-LPU26</t>
+          <t>38/1-0522-LPU26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Provisión de un kit de sistemas de fluido y mangueras aeronáuticas.</t>
+          <t>Adquisición de TRES (3) Enfriadores de Agua de Mar para Motor Generador MTU 396 TC 52-12 V</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>38/25 - Base Aeronaval Comandante espora</t>
+          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>38/25 - Base Aeronaval Comandante espora</t>
+          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3080,29 +3080,29 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>9/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>38/25-0509-LPU26</t>
+          <t>38/1-0523-LPU26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Adquisición de un kit de cabina, transparencias y accesos, con prestación de soporte técnico.</t>
+          <t>ADQ. DE LOTE DE REPUESTOS PARA MANTENIMIENTO MAYOR DE 16.000 HS MOTOR GENERADOR WARTSILA.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>38/25 - Base Aeronaval Comandante espora</t>
+          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>38/25 - Base Aeronaval Comandante espora</t>
+          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3112,29 +3112,29 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>9/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>38/25-0510-LPU26</t>
+          <t>38/27-0524-LPU26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Adquisición de un kit de estructura, tren de aterrizaje e interfaz de motor</t>
+          <t>ADQUISICIÓN DE EQUIPAMENTO ÓPTICO-ELECTRÓNICO MULTIFUNCIÓN PARA UNITAS 2027</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>38/25 - Base Aeronaval Comandante espora</t>
+          <t>38/27 - Agrupación Servicios de Cuartel</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>38/25 - Base Aeronaval Comandante espora</t>
+          <t>38/27 - Agrupación Servicios de Cuartel</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3144,29 +3144,29 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>9/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>30-0015-LPU26</t>
+          <t>38/27-0525-LPU26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Adquisición de aerosoles orgánicos OC, Granadas CS, Granadas de humo blanco y sonoro lumínicas</t>
+          <t>ADQUISICIÓN DE EQUIPOS PORTÁTILES DE VISIÓN NOCTURNA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>30/00 - División Contrataciones - Policia Federal Argentina</t>
+          <t>38/27 - Agrupación Servicios de Cuartel</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>30/00 - División Contrataciones - Policia Federal Argentina</t>
+          <t>38/27 - Agrupación Servicios de Cuartel</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3176,29 +3176,29 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>38/37-0513-LPU26</t>
+          <t>38/1-0526-LPU26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CONTRATACION DEL SERVICIO DE GUARDIA DE ANESTESIA</t>
+          <t>Prestación del serv. de prep. de sup. mediante hidrojetting y pintado en Destructor ARA SARANDI</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>38/37 - Hospital Naval Puerto Belgrano</t>
+          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>38/37 - Hospital Naval Puerto Belgrano</t>
+          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3208,29 +3208,29 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>38/37-0514-LPU26</t>
+          <t>38/27-0529-LPU26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PROVISION CONTINUA DE MODULOS PARA INTERVENCIONES QUIRURGICAS</t>
+          <t>ADQUISICIÓN DE EQUIPOS PORTÁTILES DE OBSERVACIÓN TÉRMICA E INFRARROJA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>38/37 - Hospital Naval Puerto Belgrano</t>
+          <t>38/27 - Agrupación Servicios de Cuartel</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>38/37 - Hospital Naval Puerto Belgrano</t>
+          <t>38/27 - Agrupación Servicios de Cuartel</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3239,262 +3239,6 @@
         </is>
       </c>
       <c r="F88" t="inlineStr">
-        <is>
-          <t>13/10/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>38/37-0517-LPU26</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>PROVISON CONTINUA DE SERVICIOS MEDICOS ASISTENCIALES EN GUARDIAS MEDICAS</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>38/37 - Hospital Naval Puerto Belgrano</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>38/37 - Hospital Naval Puerto Belgrano</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Publicado</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>14/10/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>38/1-0521-LPU26</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>ADQ. DE DOCE (12) LOTES DE REPUESTOS PARA SISTEMAS DE INYECCIÓN DE MOTORES DIÉSEL MTU 396 6V TC 52</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Publicado</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>15/10/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>38/1-0522-LPU26</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Adquisición de TRES (3) Enfriadores de Agua de Mar para Motor Generador MTU 396 TC 52-12 V</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Publicado</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>15/10/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>38/1-0523-LPU26</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>ADQ. DE LOTE DE REPUESTOS PARA MANTENIMIENTO MAYOR DE 16.000 HS MOTOR GENERADOR WARTSILA.</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Publicado</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>15/10/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>38/27-0524-LPU26</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>ADQUISICIÓN DE EQUIPAMENTO ÓPTICO-ELECTRÓNICO MULTIFUNCIÓN PARA UNITAS 2027</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>38/27 - Agrupación Servicios de Cuartel</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>38/27 - Agrupación Servicios de Cuartel</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Publicado</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>15/10/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>38/27-0525-LPU26</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>ADQUISICIÓN DE EQUIPOS PORTÁTILES DE VISIÓN NOCTURNA</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>38/27 - Agrupación Servicios de Cuartel</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>38/27 - Agrupación Servicios de Cuartel</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Publicado</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>15/10/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>38/1-0526-LPU26</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Prestación del serv. de prep. de sup. mediante hidrojetting y pintado en Destructor ARA SARANDI</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>38/01 - ARSENAL NAVAL PUERTO BELGRANO</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Publicado</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>15/10/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>38/27-0529-LPU26</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>ADQUISICIÓN DE EQUIPOS PORTÁTILES DE OBSERVACIÓN TÉRMICA E INFRARROJA</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>38/27 - Agrupación Servicios de Cuartel</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>38/27 - Agrupación Servicios de Cuartel</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Publicado</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
         <is>
           <t>15/10/2026</t>
         </is>
